--- a/stories/arbres/TREE-COL-007.xlsx
+++ b/stories/arbres/TREE-COL-007.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Nino arrive à l'école avec maman. La maîtresse parle. Nino aime écouter. Maman dit : tu écoutes. Si tu as un malaise, tu viens raconter à la maison. Nino range son manteau. Il s'assoit.</t>
+          <t>Nino arrive à l'école avec maman. La maîtresse parle. Nino aime écouter. Tu écoutes. Si tu as un malaise, tu viens raconter à la maison. Nino range son manteau. Il s'assoit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Nino arrive à l'école avec maman. La maîtresse parle. Nino aime écouter.
+maman|Tu écoutes. Si tu as un malaise, tu viens raconter à la maison.
+narrateur|Nino range son manteau. Il s'assoit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1511,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le tapis, la table, ou le préau.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1678,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Nino s'assoit sur le tapis. Il écoute la maîtresse. Un camarade chuchote. Nino sent un malaise. Le soir, il va raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1859,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Sur le tapis, Nino a un malaise. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1989,6 +2028,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a écouté. S'il a un malaise, il raconte à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2223,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre l'histoire, le dessin, ou la chanson.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2390,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire commence. Nino écoute. Un mot le gêne. Malaise. Il racontera à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2527,6 +2581,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2689,6 +2748,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Nino rejoint maman. Il a écouté à le tapis, pendant l'histoire. Il a eu un malaise. Il vient raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2851,6 +2915,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3013,6 +3082,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Nino rejoint papa. Il a écouté à le tapis, pendant l'histoire. Il a eu un malaise. Il vient raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3175,6 +3249,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3337,6 +3416,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Nino rejoint la sœur. Il a écouté à le tapis, pendant l'histoire. Il a eu un malaise. Il vient raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3499,6 +3583,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3661,6 +3750,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Nino dessine. Il écoute la consigne. Un chuchotement. Malaise. Raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3847,6 +3941,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4009,6 +4108,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Nino rejoint maman. Il a écouté à le tapis, pendant le dessin. Il a eu un malaise. Il vient raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4171,6 +4275,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4333,6 +4442,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Nino rejoint papa. Il a écouté à le tapis, pendant le dessin. Il a eu un malaise. Il vient raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4495,6 +4609,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4657,6 +4776,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Nino rejoint la sœur. Il a écouté à le tapis, pendant le dessin. Il a eu un malaise. Il vient raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4819,6 +4943,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4977,6 +5106,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|La chanson commence. Nino écoute. Son ventre se serre. Malaise. Il raconte à la maison le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5163,6 +5297,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5325,6 +5464,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Nino rejoint maman. Il a écouté à le tapis, pendant la chanson. Il a eu un malaise. Il vient raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5487,6 +5631,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5649,6 +5798,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Nino rejoint papa. Il a écouté à le tapis, pendant la chanson. Il a eu un malaise. Il vient raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5811,6 +5965,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5973,6 +6132,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Nino rejoint la sœur. Il a écouté à le tapis, pendant la chanson. Il a eu un malaise. Il vient raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6135,6 +6299,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6293,6 +6462,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Nino s'assoit à la table. Il écoute. Un mot le gêne. C'est un malaise. Le soir, il raconte à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6469,6 +6643,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|À la table, Nino a un malaise. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -6637,6 +6816,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Écouter. Si malaise, raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6829,6 +7013,11 @@
       <c r="AV35" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre l'histoire, le dessin, ou la chanson.</t>
         </is>
       </c>
     </row>
@@ -6993,6 +7182,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|À la table, l'histoire. Nino écoute. Malaise. Il va raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7179,6 +7373,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7341,6 +7540,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Nino rejoint maman. Il a écouté à la table, pendant l'histoire. Il a eu un malaise. Il vient raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7503,6 +7707,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7665,6 +7874,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Nino rejoint papa. Il a écouté à la table, pendant l'histoire. Il a eu un malaise. Il vient raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7827,6 +8041,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7989,6 +8208,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Nino rejoint la sœur. Il a écouté à la table, pendant l'histoire. Il a eu un malaise. Il vient raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8151,6 +8375,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8313,6 +8542,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Le dessin est posé. Nino écoute. Un malaise. Raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8499,6 +8733,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8661,6 +8900,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Nino rejoint maman. Il a écouté à la table, pendant le dessin. Il a eu un malaise. Il vient raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8823,6 +9067,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8985,6 +9234,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Nino rejoint papa. Il a écouté à la table, pendant le dessin. Il a eu un malaise. Il vient raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9147,6 +9401,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9309,6 +9568,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Nino rejoint la sœur. Il a écouté à la table, pendant le dessin. Il a eu un malaise. Il vient raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9471,6 +9735,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9629,6 +9898,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|On chante à la table. Nino écoute. Malaise. Il raconte à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9815,6 +10089,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9977,6 +10256,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Nino rejoint maman. Il a écouté à la table, pendant la chanson. Il a eu un malaise. Il vient raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10139,6 +10423,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10301,6 +10590,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Nino rejoint papa. Il a écouté à la table, pendant la chanson. Il a eu un malaise. Il vient raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10463,6 +10757,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10625,6 +10924,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Nino rejoint la sœur. Il a écouté à la table, pendant la chanson. Il a eu un malaise. Il vient raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10787,6 +11091,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10949,6 +11258,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Nino est au préau. Il écoute la maîtresse. Son ventre se serre. Un malaise. Il racontera à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11125,6 +11439,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Au préau, Nino a un malaise. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -11293,6 +11612,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Nino a su écouter. Il saura raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11485,6 +11809,11 @@
       <c r="AV63" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre l'histoire, le dessin, ou la chanson.</t>
         </is>
       </c>
     </row>
@@ -11649,6 +11978,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Au préau, l'histoire. Nino écoute. Malaise. Raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11835,6 +12169,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11997,6 +12336,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Nino rejoint maman. Il a écouté à le préau, pendant l'histoire. Il a eu un malaise. Il vient raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12159,6 +12503,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12321,6 +12670,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Nino rejoint papa. Il a écouté à le préau, pendant l'histoire. Il a eu un malaise. Il vient raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12483,6 +12837,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12645,6 +13004,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Nino rejoint la sœur. Il a écouté à le préau, pendant l'histoire. Il a eu un malaise. Il vient raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12807,6 +13171,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12969,6 +13338,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Nino dessine au préau. Il écoute. Un malaise. Il racontera à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13155,6 +13529,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13317,6 +13696,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Nino rejoint maman. Il a écouté à le préau, pendant le dessin. Il a eu un malaise. Il vient raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13479,6 +13863,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13641,6 +14030,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Nino rejoint papa. Il a écouté à le préau, pendant le dessin. Il a eu un malaise. Il vient raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13803,6 +14197,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13965,6 +14364,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Nino rejoint la sœur. Il a écouté à le préau, pendant le dessin. Il a eu un malaise. Il vient raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14127,6 +14531,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14289,6 +14698,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|La chanson au préau. Nino écoute. Malaise. Raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14475,6 +14889,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14637,6 +15056,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Nino rejoint maman. Il a écouté à le préau, pendant la chanson. Il a eu un malaise. Il vient raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14799,6 +15223,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14961,6 +15390,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Nino rejoint papa. Il a écouté à le préau, pendant la chanson. Il a eu un malaise. Il vient raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15123,6 +15557,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15285,6 +15724,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Nino rejoint la sœur. Il a écouté à le préau, pendant la chanson. Il a eu un malaise. Il vient raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15447,6 +15891,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15465,7 +15914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15489,6 +15938,13 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>ch2C: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-COL-007.xlsx
+++ b/stories/arbres/TREE-COL-007.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Nino range son manteau. Il s'assoit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1516,6 +1522,7 @@
           <t>narrateur|On peut prendre le tapis, la table, ou le préau.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1683,6 +1690,7 @@
           <t>narrateur|Nino s'assoit sur le tapis. Il écoute la maîtresse. Un camarade chuchote. Nino sent un malaise. Le soir, il va raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1866,6 +1874,7 @@
           <t>narrateur|Sur le tapis, Nino a un malaise. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2033,6 +2042,7 @@
           <t>narrateur|Nino a écouté. S'il a un malaise, il raconte à la maison.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2228,6 +2238,7 @@
           <t>narrateur|On peut prendre l'histoire, le dessin, ou la chanson.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2395,6 +2406,7 @@
           <t>narrateur|L'histoire commence. Nino écoute. Un mot le gêne. Malaise. Il racontera à la maison.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2586,6 +2598,7 @@
           <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2753,6 +2766,7 @@
           <t>narrateur|Le soir, Nino rejoint maman. Il a écouté à le tapis, pendant l'histoire. Il a eu un malaise. Il vient raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2920,6 +2934,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3087,6 +3102,7 @@
           <t>narrateur|Le soir, Nino rejoint papa. Il a écouté à le tapis, pendant l'histoire. Il a eu un malaise. Il vient raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3254,6 +3270,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3421,6 +3438,7 @@
           <t>narrateur|Le soir, Nino rejoint la sœur. Il a écouté à le tapis, pendant l'histoire. Il a eu un malaise. Il vient raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3588,6 +3606,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3755,6 +3774,7 @@
           <t>narrateur|Nino dessine. Il écoute la consigne. Un chuchotement. Malaise. Raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3946,6 +3966,7 @@
           <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4113,6 +4134,7 @@
           <t>narrateur|Le soir, Nino rejoint maman. Il a écouté à le tapis, pendant le dessin. Il a eu un malaise. Il vient raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4280,6 +4302,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4447,6 +4470,7 @@
           <t>narrateur|Le soir, Nino rejoint papa. Il a écouté à le tapis, pendant le dessin. Il a eu un malaise. Il vient raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4614,6 +4638,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4781,6 +4806,7 @@
           <t>narrateur|Le soir, Nino rejoint la sœur. Il a écouté à le tapis, pendant le dessin. Il a eu un malaise. Il vient raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4948,6 +4974,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5111,6 +5138,7 @@
           <t>narrateur|La chanson commence. Nino écoute. Son ventre se serre. Malaise. Il raconte à la maison le soir.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5302,6 +5330,7 @@
           <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5469,6 +5498,7 @@
           <t>narrateur|Le soir, Nino rejoint maman. Il a écouté à le tapis, pendant la chanson. Il a eu un malaise. Il vient raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5636,6 +5666,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5803,6 +5834,7 @@
           <t>narrateur|Le soir, Nino rejoint papa. Il a écouté à le tapis, pendant la chanson. Il a eu un malaise. Il vient raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5970,6 +6002,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6137,6 +6170,7 @@
           <t>narrateur|Le soir, Nino rejoint la sœur. Il a écouté à le tapis, pendant la chanson. Il a eu un malaise. Il vient raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6304,6 +6338,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6467,6 +6502,7 @@
           <t>narrateur|Nino s'assoit à la table. Il écoute. Un mot le gêne. C'est un malaise. Le soir, il raconte à la maison.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6650,6 +6686,7 @@
           <t>narrateur|À la table, Nino a un malaise. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6821,6 +6858,7 @@
           <t>narrateur|Oui. Écouter. Si malaise, raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7020,6 +7058,7 @@
           <t>narrateur|On peut prendre l'histoire, le dessin, ou la chanson.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7187,6 +7226,7 @@
           <t>narrateur|À la table, l'histoire. Nino écoute. Malaise. Il va raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7378,6 +7418,7 @@
           <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7545,6 +7586,7 @@
           <t>narrateur|Le soir, Nino rejoint maman. Il a écouté à la table, pendant l'histoire. Il a eu un malaise. Il vient raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7712,6 +7754,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7879,6 +7922,7 @@
           <t>narrateur|Le soir, Nino rejoint papa. Il a écouté à la table, pendant l'histoire. Il a eu un malaise. Il vient raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8046,6 +8090,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8213,6 +8258,7 @@
           <t>narrateur|Le soir, Nino rejoint la sœur. Il a écouté à la table, pendant l'histoire. Il a eu un malaise. Il vient raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8380,6 +8426,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8547,6 +8594,7 @@
           <t>narrateur|Le dessin est posé. Nino écoute. Un malaise. Raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8738,6 +8786,7 @@
           <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8905,6 +8954,7 @@
           <t>narrateur|Le soir, Nino rejoint maman. Il a écouté à la table, pendant le dessin. Il a eu un malaise. Il vient raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9072,6 +9122,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9239,6 +9290,7 @@
           <t>narrateur|Le soir, Nino rejoint papa. Il a écouté à la table, pendant le dessin. Il a eu un malaise. Il vient raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9406,6 +9458,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9573,6 +9626,7 @@
           <t>narrateur|Le soir, Nino rejoint la sœur. Il a écouté à la table, pendant le dessin. Il a eu un malaise. Il vient raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9740,6 +9794,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9903,6 +9958,7 @@
           <t>narrateur|On chante à la table. Nino écoute. Malaise. Il raconte à la maison.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10094,6 +10150,7 @@
           <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10261,6 +10318,7 @@
           <t>narrateur|Le soir, Nino rejoint maman. Il a écouté à la table, pendant la chanson. Il a eu un malaise. Il vient raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10428,6 +10486,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10595,6 +10654,7 @@
           <t>narrateur|Le soir, Nino rejoint papa. Il a écouté à la table, pendant la chanson. Il a eu un malaise. Il vient raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10762,6 +10822,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10929,6 +10990,7 @@
           <t>narrateur|Le soir, Nino rejoint la sœur. Il a écouté à la table, pendant la chanson. Il a eu un malaise. Il vient raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11096,6 +11158,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11263,6 +11326,7 @@
           <t>narrateur|Nino est au préau. Il écoute la maîtresse. Son ventre se serre. Un malaise. Il racontera à la maison.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11446,6 +11510,7 @@
           <t>narrateur|Au préau, Nino a un malaise. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11617,6 +11682,7 @@
           <t>narrateur|Nino a su écouter. Il saura raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11816,6 +11882,7 @@
           <t>narrateur|On peut prendre l'histoire, le dessin, ou la chanson.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11983,6 +12050,7 @@
           <t>narrateur|Au préau, l'histoire. Nino écoute. Malaise. Raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12174,6 +12242,7 @@
           <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12341,6 +12410,7 @@
           <t>narrateur|Le soir, Nino rejoint maman. Il a écouté à le préau, pendant l'histoire. Il a eu un malaise. Il vient raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12508,6 +12578,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12675,6 +12746,7 @@
           <t>narrateur|Le soir, Nino rejoint papa. Il a écouté à le préau, pendant l'histoire. Il a eu un malaise. Il vient raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12842,6 +12914,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13009,6 +13082,7 @@
           <t>narrateur|Le soir, Nino rejoint la sœur. Il a écouté à le préau, pendant l'histoire. Il a eu un malaise. Il vient raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13176,6 +13250,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13343,6 +13418,7 @@
           <t>narrateur|Nino dessine au préau. Il écoute. Un malaise. Il racontera à la maison.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13534,6 +13610,7 @@
           <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13701,6 +13778,7 @@
           <t>narrateur|Le soir, Nino rejoint maman. Il a écouté à le préau, pendant le dessin. Il a eu un malaise. Il vient raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13868,6 +13946,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14035,6 +14114,7 @@
           <t>narrateur|Le soir, Nino rejoint papa. Il a écouté à le préau, pendant le dessin. Il a eu un malaise. Il vient raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14202,6 +14282,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14369,6 +14450,7 @@
           <t>narrateur|Le soir, Nino rejoint la sœur. Il a écouté à le préau, pendant le dessin. Il a eu un malaise. Il vient raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14536,6 +14618,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14703,6 +14786,7 @@
           <t>narrateur|La chanson au préau. Nino écoute. Malaise. Raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14894,6 +14978,7 @@
           <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15061,6 +15146,7 @@
           <t>narrateur|Le soir, Nino rejoint maman. Il a écouté à le préau, pendant la chanson. Il a eu un malaise. Il vient raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15228,6 +15314,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15395,6 +15482,7 @@
           <t>narrateur|Le soir, Nino rejoint papa. Il a écouté à le préau, pendant la chanson. Il a eu un malaise. Il vient raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15562,6 +15650,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15729,6 +15818,7 @@
           <t>narrateur|Le soir, Nino rejoint la sœur. Il a écouté à le préau, pendant la chanson. Il a eu un malaise. Il vient raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15896,6 +15986,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15914,7 +16005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15945,6 +16036,20 @@
       <c r="A4" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15959,7 +16064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16146,6 +16251,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-COL-007.xlsx
+++ b/stories/arbres/TREE-COL-007.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nino écoute, puis raconte à la maison</t>
+          <t>La porte embuée et les bottes de Nino</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Après la pluie, Nino laisse ses bottes près du radiateur. Il écoute la maîtresse. Un chuchotement serre son ventre. Le soir, il raconte à la maison, à maman, à papa, ou à Sarah.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Nino arrive à l'école avec maman. La maîtresse parle. Nino aime écouter. Tu écoutes. Si tu as un malaise, tu viens raconter à la maison. Nino range son manteau. Il s'assoit.</t>
+          <t>La porte vitrée de l'école est encore embuée. Derrière, une flaque ronde brille. Un moineau secoue ses plumes, tout vite. Ça sent la laine mouillée, dans le couloir. Le radiateur fait tic, tic, tout bas. Les crochets des manteaux sont froids. Un bouton jaune pend sur un caban bleu. Tes bottes, Nino. Elles gouttent encore. Elles sont lourdes. On les pose près du radiateur. Deux petites traces sombres restent au sol. Un bonnet rouge attend sur le banc. Sarah l'a oublié, ce matin. Il est encore humide. On le ramène ce soir. En ce moment, Nino accroche son manteau. Le zip fait un petit bruit. Tu écoutes la maîtresse, d'accord ? Oui. J'écoute. Si tu as un malaise, tu racontes à la maison. Je raconte à la maison. Bravo, Nino. C'est du bon travail. Une goutte tombe du manteau, tout doux. On vient te chercher plus tard. D'accord, papa. Le moineau a disparu. La flaque reste.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,12 +1337,43 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Nino arrive à l'école avec maman. La maîtresse parle. Nino aime écouter.
-maman|Tu écoutes. Si tu as un malaise, tu viens raconter à la maison.
-narrateur|Nino range son manteau. Il s'assoit.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La porte vitrée de l'école est encore embuée.
+narrateur|Derrière, une flaque ronde brille.
+narrateur|Un moineau secoue ses plumes, tout vite.
+narrateur|Ça sent la laine mouillée, dans le couloir.
+narrateur|Le radiateur fait tic, tic, tout bas.
+narrateur|Les crochets des manteaux sont froids.
+narrateur|Un bouton jaune pend sur un caban bleu.
+maman|Tes bottes, Nino.
+maman|Elles gouttent encore.
+enfant-m|Elles sont lourdes.
+papa|On les pose près du radiateur.
+narrateur|Deux petites traces sombres restent au sol.
+narrateur|Un bonnet rouge attend sur le banc.
+maman|Sarah l'a oublié, ce matin.
+enfant-m|Il est encore humide.
+papa|On le ramène ce soir.
+narrateur|En ce moment, Nino accroche son manteau.
+narrateur|Le zip fait un petit bruit.
+maman|Tu écoutes la maîtresse, d'accord ?
+enfant-m|Oui.
+enfant-m|J'écoute.
+papa|Si tu as un malaise, tu racontes à la maison.
+enfant-m|Je raconte à la maison.
+maman|Bravo, Nino.
+maman|C'est du bon travail.
+narrateur|Une goutte tombe du manteau, tout doux.
+papa|On vient te chercher plus tard.
+enfant-m|D'accord, papa.
+narrateur|Le moineau a disparu.
+narrateur|La flaque reste.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>radiateur,manteau</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1355,7 +1398,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le tapis, la table, ou le préau.</t>
+          <t>Nino peut s'asseoir à trois endroits. Le tapis, la table, ou le préau ? Choisis. Ensuite on écoute.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1519,7 +1562,10 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le tapis, la table, ou le préau.</t>
+          <t>narrateur|Nino peut s'asseoir à trois endroits.
+papa|Le tapis, la table, ou le préau ?
+maman|Choisis.
+maman|Ensuite on écoute.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1547,7 +1593,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nino s'assoit sur le tapis. Il écoute la maîtresse. Un camarade chuchote. Nino sent un malaise. Le soir, il va raconter à la maison.</t>
+          <t>Nino pose les genoux sur le tapis. Le tapis est épais, un peu rêche. Il a des carrés bleus et gris. Ça sent la poussière et le savon. La maîtresse parle, tout doux. Nino écoute chaque mot. Un camarade chuchote près de l'oreille. Le ventre de Nino se serre, tout petit. J'ai un malaise. Tu as écouté la maîtresse. Ce soir, tu racontes à la maison. On t'écoutera, Nino. Je raconte à la maison. Bravo. C'est du bon travail. Une fibre du tapis brille, sous le soleil.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1687,10 +1733,29 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Nino s'assoit sur le tapis. Il écoute la maîtresse. Un camarade chuchote. Nino sent un malaise. Le soir, il va raconter à la maison.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nino pose les genoux sur le tapis.
+narrateur|Le tapis est épais, un peu rêche.
+narrateur|Il a des carrés bleus et gris.
+narrateur|Ça sent la poussière et le savon.
+narrateur|La maîtresse parle, tout doux.
+narrateur|Nino écoute chaque mot.
+narrateur|Un camarade chuchote près de l'oreille.
+narrateur|Le ventre de Nino se serre, tout petit.
+enfant-m|J'ai un malaise.
+maman|Tu as écouté la maîtresse.
+maman|Ce soir, tu racontes à la maison.
+papa|On t'écoutera, Nino.
+enfant-m|Je raconte à la maison.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|Une fibre du tapis brille, sous le soleil.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>tapis</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1871,7 +1936,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Sur le tapis, Nino a un malaise. Que fait-il ?</t>
+          <t>narrateur|Sur le tapis, Nino a un malaise.
+maman|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1899,7 +1965,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Nino a écouté. S'il a un malaise, il raconte à la maison.</t>
+          <t>Oui. On écoute la maîtresse. Si malaise, raconter à la maison. Nino respire, tout calme. Bravo, Nino. Tu as fait du bon travail. Je raconte à la maison.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2039,7 +2105,13 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Nino a écouté. S'il a un malaise, il raconte à la maison.</t>
+          <t>narrateur|Oui.
+maman|On écoute la maîtresse.
+papa|Si malaise, raconter à la maison.
+narrateur|Nino respire, tout calme.
+maman|Bravo, Nino.
+maman|Tu as fait du bon travail.
+enfant-m|Je raconte à la maison.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2067,7 +2139,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre l'histoire, le dessin, ou la chanson.</t>
+          <t>La classe continue, tout doux. L'histoire, le dessin, ou la chanson ? On prend ça. Puis on raconte.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2235,7 +2307,10 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre l'histoire, le dessin, ou la chanson.</t>
+          <t>narrateur|La classe continue, tout doux.
+maman|L'histoire, le dessin, ou la chanson ?
+papa|On prend ça.
+papa|Puis on raconte.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2263,7 +2338,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>L'histoire commence. Nino écoute. Un mot le gêne. Malaise. Il racontera à la maison.</t>
+          <t>Sur le tapis, la maîtresse ouvre un livre. La couverture est jaune, un peu usée. Nino pose les mains à plat. Il écoute l'histoire, jusqu'au bout. Un mot le gêne. Le ventre se serre. Je raconterai à la maison. Plus tard, la porte de l'école s'ouvre. Je suis là, Nino. J'ai un malaise, maman. Tu as écouté. Tu nous le diras. À la maison, on t'écoute. Le livre jaune reste dans sa tête.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2403,10 +2478,27 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire commence. Nino écoute. Un mot le gêne. Malaise. Il racontera à la maison.</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr"/>
+          <t>narrateur|Sur le tapis, la maîtresse ouvre un livre.
+narrateur|La couverture est jaune, un peu usée.
+narrateur|Nino pose les mains à plat.
+narrateur|Il écoute l'histoire, jusqu'au bout.
+narrateur|Un mot le gêne.
+narrateur|Le ventre se serre.
+enfant-m|Je raconterai à la maison.
+narrateur|Plus tard, la porte de l'école s'ouvre.
+maman|Je suis là, Nino.
+enfant-m|J'ai un malaise, maman.
+papa|Tu as écouté.
+papa|Tu nous le diras.
+maman|À la maison, on t'écoute.
+narrateur|Le livre jaune reste dans sa tête.</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2431,7 +2523,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre maman, papa, ou la sœur.</t>
+          <t>Le soir, Nino raconte à quelqu'un. Maman, papa, ou Sarah ? Choisis. On t'écoute.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2595,7 +2687,10 @@
       <c r="AV9" s="2" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+          <t>narrateur|Le soir, Nino raconte à quelqu'un.
+maman|Maman, papa, ou Sarah ?
+papa|Choisis.
+papa|On t'écoute.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2623,7 +2718,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Nino rejoint maman. Il a écouté à le tapis, pendant l'histoire. Il a eu un malaise. Il vient raconter à la maison.</t>
+          <t>Le soir, la maison sent la soupe. La lampe fait un rond jaune. Nino rejoint maman, près de la casserole. Il a écouté sur le tapis, pendant l'histoire. Maman, j'ai un malaise. Un camarade a parlé tout bas. Tu as bien fait de raconter. Tu as écouté la maîtresse. Si tu as un malaise, tu viens nous le dire. Je raconte à la maison. Bravo, Nino. C'est du bon travail. Je t'écoute. On reste un moment. Une fibre bleue du tapis brille sous la lampe. Le ventre de Nino se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2763,10 +2858,29 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Nino rejoint maman. Il a écouté à le tapis, pendant l'histoire. Il a eu un malaise. Il vient raconter à la maison.</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr"/>
+          <t>narrateur|Le soir, la maison sent la soupe.
+narrateur|La lampe fait un rond jaune.
+narrateur|Nino rejoint maman, près de la casserole.
+narrateur|Il a écouté sur le tapis, pendant l'histoire.
+enfant-m|Maman, j'ai un malaise.
+enfant-m|Un camarade a parlé tout bas.
+maman|Tu as bien fait de raconter.
+maman|Tu as écouté la maîtresse.
+papa|Si tu as un malaise, tu viens nous le dire.
+enfant-m|Je raconte à la maison.
+maman|Bravo, Nino.
+maman|C'est du bon travail.
+papa|Je t'écoute.
+papa|On reste un moment.
+narrateur|Une fibre bleue du tapis brille sous la lampe.
+narrateur|Le ventre de Nino se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>soupe</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2791,7 +2905,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nino a écouté sur le tapis, pendant l'histoire. Puis il a raconté, à maman. Le tapis bleu reste dans sa tête. Le livre jaune est fermé, tout calme. Maman pose la main sur son épaule. J'ai écouté. Puis j'ai raconté. Bravo, Nino. Tu as fait du bon travail. On t'a écouté. Si malaise, tu reviens nous le dire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2931,7 +3045,18 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nino a écouté sur le tapis, pendant l'histoire.
+narrateur|Puis il a raconté, à maman.
+narrateur|Le tapis bleu reste dans sa tête.
+narrateur|Le livre jaune est fermé, tout calme.
+narrateur|Maman pose la main sur son épaule.
+enfant-m|J'ai écouté.
+enfant-m|Puis j'ai raconté.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+maman|On t'a écouté.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2959,7 +3084,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Nino rejoint papa. Il a écouté à le tapis, pendant l'histoire. Il a eu un malaise. Il vient raconter à la maison.</t>
+          <t>Le soir, la maison sent la soupe. La lampe fait un rond jaune. Nino rejoint papa, près du cacao. Il a écouté sur le tapis, pendant l'histoire. Papa, j'ai un malaise. Un mot m'a gêné, à l'école. Tu as bien fait de le dire. Tu as écouté la maîtresse. Si malaise, tu racontes à la maison. Je raconte à papa et maman. Bravo, Nino. Tu as fait du bon travail. On t'écoute. Ton ventre peut se desserrer. Papa pose le livre oublié sur la table. Le ventre de Nino se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3099,10 +3224,29 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Nino rejoint papa. Il a écouté à le tapis, pendant l'histoire. Il a eu un malaise. Il vient raconter à la maison.</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr"/>
+          <t>narrateur|Le soir, la maison sent la soupe.
+narrateur|La lampe fait un rond jaune.
+narrateur|Nino rejoint papa, près du cacao.
+narrateur|Il a écouté sur le tapis, pendant l'histoire.
+enfant-m|Papa, j'ai un malaise.
+enfant-m|Un mot m'a gêné, à l'école.
+papa|Tu as bien fait de le dire.
+papa|Tu as écouté la maîtresse.
+maman|Si malaise, tu racontes à la maison.
+enfant-m|Je raconte à papa et maman.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+maman|On t'écoute.
+maman|Ton ventre peut se desserrer.
+narrateur|Papa pose le livre oublié sur la table.
+narrateur|Le ventre de Nino se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>cacao</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3127,7 +3271,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nino a écouté sur le tapis, pendant l'histoire. Puis il a raconté, à papa. Le tapis bleu reste dans sa tête. Le livre jaune est fermé, tout calme. Papa souffle sur le cacao, tout doux. J'ai écouté. Puis j'ai raconté. Bravo, Nino. Tu as fait du bon travail. On t'a écouté. Si malaise, tu reviens nous le dire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3267,7 +3411,18 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nino a écouté sur le tapis, pendant l'histoire.
+narrateur|Puis il a raconté, à papa.
+narrateur|Le tapis bleu reste dans sa tête.
+narrateur|Le livre jaune est fermé, tout calme.
+narrateur|Papa souffle sur le cacao, tout doux.
+enfant-m|J'ai écouté.
+enfant-m|Puis j'ai raconté.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+maman|On t'a écouté.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3295,7 +3450,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Nino rejoint la sœur. Il a écouté à le tapis, pendant l'histoire. Il a eu un malaise. Il vient raconter à la maison.</t>
+          <t>Le soir, la maison sent la soupe. La lampe fait un rond jaune. Nino rejoint Sarah, près du bol de Sarah. Il a écouté sur le tapis, pendant l'histoire. Sarah, j'ai un malaise. Je t'écoute, Nino. Un camarade a chuchoté. Nino veut raconter. Tu as écouté la maîtresse. Si malaise, raconter à la maison. Je raconte à la maison. Bravo, les enfants. C'est du bon travail. Sarah touche la page, tout doux, du doigt. Le ventre de Nino se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3435,10 +3590,28 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Nino rejoint la sœur. Il a écouté à le tapis, pendant l'histoire. Il a eu un malaise. Il vient raconter à la maison.</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr"/>
+          <t>narrateur|Le soir, la maison sent la soupe.
+narrateur|La lampe fait un rond jaune.
+narrateur|Nino rejoint Sarah, près du bol de Sarah.
+narrateur|Il a écouté sur le tapis, pendant l'histoire.
+enfant-m|Sarah, j'ai un malaise.
+enfant-f|Je t'écoute, Nino.
+enfant-m|Un camarade a chuchoté.
+enfant-f|Nino veut raconter.
+maman|Tu as écouté la maîtresse.
+papa|Si malaise, raconter à la maison.
+enfant-m|Je raconte à la maison.
+maman|Bravo, les enfants.
+maman|C'est du bon travail.
+narrateur|Sarah touche la page, tout doux, du doigt.
+narrateur|Le ventre de Nino se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>bol</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3463,7 +3636,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nino a écouté sur le tapis, pendant l'histoire. Puis il a raconté, à Sarah. Le tapis bleu reste dans sa tête. Le livre jaune est fermé, tout calme. Sarah pousse son bol vers Nino. J'ai écouté. Puis j'ai raconté. Bravo, Nino. Tu as fait du bon travail. On t'a écouté. Si malaise, tu reviens nous le dire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3603,7 +3776,18 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nino a écouté sur le tapis, pendant l'histoire.
+narrateur|Puis il a raconté, à Sarah.
+narrateur|Le tapis bleu reste dans sa tête.
+narrateur|Le livre jaune est fermé, tout calme.
+narrateur|Sarah pousse son bol vers Nino.
+enfant-m|J'ai écouté.
+enfant-m|Puis j'ai raconté.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+maman|On t'a écouté.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3631,7 +3815,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Nino dessine. Il écoute la consigne. Un chuchotement. Malaise. Raconter à la maison.</t>
+          <t>Sur le tapis, une feuille attend. Le crayon rouge est un peu gras. Nino écoute la consigne. Un camarade chuchote. Le ventre se serre. C'est un malaise. Plus tard, maman est près de la porte. Tu as dessiné, Nino ? Oui. J'ai un malaise aussi. Tu as écouté. Tu racontes à la maison. Bravo. On t'écoute, ce soir. Le crayon a laissé un petit rond.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3771,10 +3955,28 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Nino dessine. Il écoute la consigne. Un chuchotement. Malaise. Raconter à la maison.</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr"/>
+          <t>narrateur|Sur le tapis, une feuille attend.
+narrateur|Le crayon rouge est un peu gras.
+narrateur|Nino écoute la consigne.
+narrateur|Un camarade chuchote.
+narrateur|Le ventre se serre.
+enfant-m|C'est un malaise.
+narrateur|Plus tard, maman est près de la porte.
+maman|Tu as dessiné, Nino ?
+enfant-m|Oui.
+enfant-m|J'ai un malaise aussi.
+papa|Tu as écouté.
+papa|Tu racontes à la maison.
+maman|Bravo.
+maman|On t'écoute, ce soir.
+narrateur|Le crayon a laissé un petit rond.</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>crayon</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3799,7 +4001,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre maman, papa, ou la sœur.</t>
+          <t>Le soir, Nino raconte à quelqu'un. Maman, papa, ou Sarah ? Choisis. On t'écoute.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3963,7 +4165,10 @@
       <c r="AV17" s="2" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+          <t>narrateur|Le soir, Nino raconte à quelqu'un.
+maman|Maman, papa, ou Sarah ?
+papa|Choisis.
+papa|On t'écoute.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -3991,7 +4196,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Nino rejoint maman. Il a écouté à le tapis, pendant le dessin. Il a eu un malaise. Il vient raconter à la maison.</t>
+          <t>Le soir, la maison sent la soupe. La lampe fait un rond jaune. Nino rejoint maman, près de la casserole. Il a écouté sur le tapis, pendant le dessin. Maman, j'ai un malaise. Un camarade a parlé tout bas. Tu as bien fait de raconter. Tu as écouté la maîtresse. Si tu as un malaise, tu viens nous le dire. Je raconte à la maison. Bravo, Nino. C'est du bon travail. Je t'écoute. On reste un moment. Une mine rouge a taché un peu le doigt de Nino. Le ventre de Nino se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4131,10 +4336,29 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Nino rejoint maman. Il a écouté à le tapis, pendant le dessin. Il a eu un malaise. Il vient raconter à la maison.</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr"/>
+          <t>narrateur|Le soir, la maison sent la soupe.
+narrateur|La lampe fait un rond jaune.
+narrateur|Nino rejoint maman, près de la casserole.
+narrateur|Il a écouté sur le tapis, pendant le dessin.
+enfant-m|Maman, j'ai un malaise.
+enfant-m|Un camarade a parlé tout bas.
+maman|Tu as bien fait de raconter.
+maman|Tu as écouté la maîtresse.
+papa|Si tu as un malaise, tu viens nous le dire.
+enfant-m|Je raconte à la maison.
+maman|Bravo, Nino.
+maman|C'est du bon travail.
+papa|Je t'écoute.
+papa|On reste un moment.
+narrateur|Une mine rouge a taché un peu le doigt de Nino.
+narrateur|Le ventre de Nino se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>soupe</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4159,7 +4383,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nino a écouté sur le tapis, pendant le dessin. Puis il a raconté, à maman. Le tapis bleu reste dans sa tête. Le crayon rouge repose, tout calme. Maman pose la main sur son épaule. J'ai écouté. Puis j'ai raconté. Bravo, Nino. Tu as fait du bon travail. On t'a écouté. Si malaise, tu reviens nous le dire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4299,7 +4523,18 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nino a écouté sur le tapis, pendant le dessin.
+narrateur|Puis il a raconté, à maman.
+narrateur|Le tapis bleu reste dans sa tête.
+narrateur|Le crayon rouge repose, tout calme.
+narrateur|Maman pose la main sur son épaule.
+enfant-m|J'ai écouté.
+enfant-m|Puis j'ai raconté.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+maman|On t'a écouté.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4327,7 +4562,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Nino rejoint papa. Il a écouté à le tapis, pendant le dessin. Il a eu un malaise. Il vient raconter à la maison.</t>
+          <t>Le soir, la maison sent la soupe. La lampe fait un rond jaune. Nino rejoint papa, près du cacao. Il a écouté sur le tapis, pendant le dessin. Papa, j'ai un malaise. Un mot m'a gêné, à l'école. Tu as bien fait de le dire. Tu as écouté la maîtresse. Si malaise, tu racontes à la maison. Je raconte à papa et maman. Bravo, Nino. Tu as fait du bon travail. On t'écoute. Ton ventre peut se desserrer. Papa essuie la mine rouge, sans rien dire fort. Le ventre de Nino se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4467,10 +4702,29 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Nino rejoint papa. Il a écouté à le tapis, pendant le dessin. Il a eu un malaise. Il vient raconter à la maison.</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr"/>
+          <t>narrateur|Le soir, la maison sent la soupe.
+narrateur|La lampe fait un rond jaune.
+narrateur|Nino rejoint papa, près du cacao.
+narrateur|Il a écouté sur le tapis, pendant le dessin.
+enfant-m|Papa, j'ai un malaise.
+enfant-m|Un mot m'a gêné, à l'école.
+papa|Tu as bien fait de le dire.
+papa|Tu as écouté la maîtresse.
+maman|Si malaise, tu racontes à la maison.
+enfant-m|Je raconte à papa et maman.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+maman|On t'écoute.
+maman|Ton ventre peut se desserrer.
+narrateur|Papa essuie la mine rouge, sans rien dire fort.
+narrateur|Le ventre de Nino se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>cacao</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4495,7 +4749,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nino a écouté sur le tapis, pendant le dessin. Puis il a raconté, à papa. Le tapis bleu reste dans sa tête. Le crayon rouge repose, tout calme. Papa souffle sur le cacao, tout doux. J'ai écouté. Puis j'ai raconté. Bravo, Nino. Tu as fait du bon travail. On t'a écouté. Si malaise, tu reviens nous le dire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4635,7 +4889,18 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nino a écouté sur le tapis, pendant le dessin.
+narrateur|Puis il a raconté, à papa.
+narrateur|Le tapis bleu reste dans sa tête.
+narrateur|Le crayon rouge repose, tout calme.
+narrateur|Papa souffle sur le cacao, tout doux.
+enfant-m|J'ai écouté.
+enfant-m|Puis j'ai raconté.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+maman|On t'a écouté.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4663,7 +4928,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Nino rejoint la sœur. Il a écouté à le tapis, pendant le dessin. Il a eu un malaise. Il vient raconter à la maison.</t>
+          <t>Le soir, la maison sent la soupe. La lampe fait un rond jaune. Nino rejoint Sarah, près du bol de Sarah. Il a écouté sur le tapis, pendant le dessin. Sarah, j'ai un malaise. Je t'écoute, Nino. Un camarade a chuchoté. Nino veut raconter. Tu as écouté la maîtresse. Si malaise, raconter à la maison. Je raconte à la maison. Bravo, les enfants. C'est du bon travail. Sarah montre un rond, sur la feuille pliée. Le ventre de Nino se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4803,10 +5068,28 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Nino rejoint la sœur. Il a écouté à le tapis, pendant le dessin. Il a eu un malaise. Il vient raconter à la maison.</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr"/>
+          <t>narrateur|Le soir, la maison sent la soupe.
+narrateur|La lampe fait un rond jaune.
+narrateur|Nino rejoint Sarah, près du bol de Sarah.
+narrateur|Il a écouté sur le tapis, pendant le dessin.
+enfant-m|Sarah, j'ai un malaise.
+enfant-f|Je t'écoute, Nino.
+enfant-m|Un camarade a chuchoté.
+enfant-f|Nino veut raconter.
+maman|Tu as écouté la maîtresse.
+papa|Si malaise, raconter à la maison.
+enfant-m|Je raconte à la maison.
+maman|Bravo, les enfants.
+maman|C'est du bon travail.
+narrateur|Sarah montre un rond, sur la feuille pliée.
+narrateur|Le ventre de Nino se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>bol</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4831,7 +5114,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nino a écouté sur le tapis, pendant le dessin. Puis il a raconté, à Sarah. Le tapis bleu reste dans sa tête. Le crayon rouge repose, tout calme. Sarah pousse son bol vers Nino. J'ai écouté. Puis j'ai raconté. Bravo, Nino. Tu as fait du bon travail. On t'a écouté. Si malaise, tu reviens nous le dire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4971,7 +5254,18 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nino a écouté sur le tapis, pendant le dessin.
+narrateur|Puis il a raconté, à Sarah.
+narrateur|Le tapis bleu reste dans sa tête.
+narrateur|Le crayon rouge repose, tout calme.
+narrateur|Sarah pousse son bol vers Nino.
+enfant-m|J'ai écouté.
+enfant-m|Puis j'ai raconté.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+maman|On t'a écouté.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -4999,7 +5293,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>La chanson commence. Nino écoute. Son ventre se serre. Malaise. Il raconte à la maison le soir.</t>
+          <t>Sur le tapis, la chanson commence. Les mains tapent, tout doux. Nino écoute. Il chante un peu. Son ventre se serre, au milieu d'un mot. J'ai un malaise. Plus tard, papa attend sous le préau. Je t'ai entendu chanter, Nino. Papa, mon ventre est serré. Tu as écouté. Tu racontes à la maison. On t'écoute. Viens. Un dernier air reste, dans le couloir.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5135,10 +5429,27 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|La chanson commence. Nino écoute. Son ventre se serre. Malaise. Il raconte à la maison le soir.</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr"/>
+          <t>narrateur|Sur le tapis, la chanson commence.
+narrateur|Les mains tapent, tout doux.
+narrateur|Nino écoute.
+narrateur|Il chante un peu.
+narrateur|Son ventre se serre, au milieu d'un mot.
+enfant-m|J'ai un malaise.
+narrateur|Plus tard, papa attend sous le préau.
+papa|Je t'ai entendu chanter, Nino.
+enfant-m|Papa, mon ventre est serré.
+maman|Tu as écouté.
+maman|Tu racontes à la maison.
+papa|On t'écoute.
+papa|Viens.
+narrateur|Un dernier air reste, dans le couloir.</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>voix_enfant</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5163,7 +5474,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre maman, papa, ou la sœur.</t>
+          <t>Le soir, Nino raconte à quelqu'un. Maman, papa, ou Sarah ? Choisis. On t'écoute.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5327,7 +5638,10 @@
       <c r="AV25" s="2" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+          <t>narrateur|Le soir, Nino raconte à quelqu'un.
+maman|Maman, papa, ou Sarah ?
+papa|Choisis.
+papa|On t'écoute.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5355,7 +5669,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Nino rejoint maman. Il a écouté à le tapis, pendant la chanson. Il a eu un malaise. Il vient raconter à la maison.</t>
+          <t>Le soir, la maison sent la soupe. La lampe fait un rond jaune. Nino rejoint maman, près de la casserole. Il a écouté sur le tapis, pendant la chanson. Maman, j'ai un malaise. Un camarade a parlé tout bas. Tu as bien fait de raconter. Tu as écouté la maîtresse. Si tu as un malaise, tu viens nous le dire. Je raconte à la maison. Bravo, Nino. C'est du bon travail. Je t'écoute. On reste un moment. Maman fredonne un tout petit bout de chanson. Le ventre de Nino se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5495,10 +5809,29 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Nino rejoint maman. Il a écouté à le tapis, pendant la chanson. Il a eu un malaise. Il vient raconter à la maison.</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr"/>
+          <t>narrateur|Le soir, la maison sent la soupe.
+narrateur|La lampe fait un rond jaune.
+narrateur|Nino rejoint maman, près de la casserole.
+narrateur|Il a écouté sur le tapis, pendant la chanson.
+enfant-m|Maman, j'ai un malaise.
+enfant-m|Un camarade a parlé tout bas.
+maman|Tu as bien fait de raconter.
+maman|Tu as écouté la maîtresse.
+papa|Si tu as un malaise, tu viens nous le dire.
+enfant-m|Je raconte à la maison.
+maman|Bravo, Nino.
+maman|C'est du bon travail.
+papa|Je t'écoute.
+papa|On reste un moment.
+narrateur|Maman fredonne un tout petit bout de chanson.
+narrateur|Le ventre de Nino se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>soupe</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5523,7 +5856,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nino a écouté sur le tapis, pendant la chanson. Puis il a raconté, à maman. Le tapis bleu reste dans sa tête. La chanson s'est tue, tout doux. Maman pose la main sur son épaule. J'ai écouté. Puis j'ai raconté. Bravo, Nino. Tu as fait du bon travail. On t'a écouté. Si malaise, tu reviens nous le dire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5663,7 +5996,18 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nino a écouté sur le tapis, pendant la chanson.
+narrateur|Puis il a raconté, à maman.
+narrateur|Le tapis bleu reste dans sa tête.
+narrateur|La chanson s'est tue, tout doux.
+narrateur|Maman pose la main sur son épaule.
+enfant-m|J'ai écouté.
+enfant-m|Puis j'ai raconté.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+maman|On t'a écouté.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5691,7 +6035,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Nino rejoint papa. Il a écouté à le tapis, pendant la chanson. Il a eu un malaise. Il vient raconter à la maison.</t>
+          <t>Le soir, la maison sent la soupe. La lampe fait un rond jaune. Nino rejoint papa, près du cacao. Il a écouté sur le tapis, pendant la chanson. Papa, j'ai un malaise. Un mot m'a gêné, à l'école. Tu as bien fait de le dire. Tu as écouté la maîtresse. Si malaise, tu racontes à la maison. Je raconte à papa et maman. Bravo, Nino. Tu as fait du bon travail. On t'écoute. Ton ventre peut se desserrer. Papa tape deux fois, très doux, sur la table. Le ventre de Nino se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5831,10 +6175,29 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Nino rejoint papa. Il a écouté à le tapis, pendant la chanson. Il a eu un malaise. Il vient raconter à la maison.</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr"/>
+          <t>narrateur|Le soir, la maison sent la soupe.
+narrateur|La lampe fait un rond jaune.
+narrateur|Nino rejoint papa, près du cacao.
+narrateur|Il a écouté sur le tapis, pendant la chanson.
+enfant-m|Papa, j'ai un malaise.
+enfant-m|Un mot m'a gêné, à l'école.
+papa|Tu as bien fait de le dire.
+papa|Tu as écouté la maîtresse.
+maman|Si malaise, tu racontes à la maison.
+enfant-m|Je raconte à papa et maman.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+maman|On t'écoute.
+maman|Ton ventre peut se desserrer.
+narrateur|Papa tape deux fois, très doux, sur la table.
+narrateur|Le ventre de Nino se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>cacao</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5859,7 +6222,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nino a écouté sur le tapis, pendant la chanson. Puis il a raconté, à papa. Le tapis bleu reste dans sa tête. La chanson s'est tue, tout doux. Papa souffle sur le cacao, tout doux. J'ai écouté. Puis j'ai raconté. Bravo, Nino. Tu as fait du bon travail. On t'a écouté. Si malaise, tu reviens nous le dire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -5999,7 +6362,18 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nino a écouté sur le tapis, pendant la chanson.
+narrateur|Puis il a raconté, à papa.
+narrateur|Le tapis bleu reste dans sa tête.
+narrateur|La chanson s'est tue, tout doux.
+narrateur|Papa souffle sur le cacao, tout doux.
+enfant-m|J'ai écouté.
+enfant-m|Puis j'ai raconté.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+maman|On t'a écouté.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6027,7 +6401,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Nino rejoint la sœur. Il a écouté à le tapis, pendant la chanson. Il a eu un malaise. Il vient raconter à la maison.</t>
+          <t>Le soir, la maison sent la soupe. La lampe fait un rond jaune. Nino rejoint Sarah, près du bol de Sarah. Il a écouté sur le tapis, pendant la chanson. Sarah, j'ai un malaise. Je t'écoute, Nino. Un camarade a chuchoté. Nino veut raconter. Tu as écouté la maîtresse. Si malaise, raconter à la maison. Je raconte à la maison. Bravo, les enfants. C'est du bon travail. Sarah chante tout bas, juste pour Nino. Le ventre de Nino se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6167,10 +6541,28 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Nino rejoint la sœur. Il a écouté à le tapis, pendant la chanson. Il a eu un malaise. Il vient raconter à la maison.</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr"/>
+          <t>narrateur|Le soir, la maison sent la soupe.
+narrateur|La lampe fait un rond jaune.
+narrateur|Nino rejoint Sarah, près du bol de Sarah.
+narrateur|Il a écouté sur le tapis, pendant la chanson.
+enfant-m|Sarah, j'ai un malaise.
+enfant-f|Je t'écoute, Nino.
+enfant-m|Un camarade a chuchoté.
+enfant-f|Nino veut raconter.
+maman|Tu as écouté la maîtresse.
+papa|Si malaise, raconter à la maison.
+enfant-m|Je raconte à la maison.
+maman|Bravo, les enfants.
+maman|C'est du bon travail.
+narrateur|Sarah chante tout bas, juste pour Nino.
+narrateur|Le ventre de Nino se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>bol</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6195,7 +6587,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nino a écouté sur le tapis, pendant la chanson. Puis il a raconté, à Sarah. Le tapis bleu reste dans sa tête. La chanson s'est tue, tout doux. Sarah pousse son bol vers Nino. J'ai écouté. Puis j'ai raconté. Bravo, Nino. Tu as fait du bon travail. On t'a écouté. Si malaise, tu reviens nous le dire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6335,7 +6727,18 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nino a écouté sur le tapis, pendant la chanson.
+narrateur|Puis il a raconté, à Sarah.
+narrateur|Le tapis bleu reste dans sa tête.
+narrateur|La chanson s'est tue, tout doux.
+narrateur|Sarah pousse son bol vers Nino.
+enfant-m|J'ai écouté.
+enfant-m|Puis j'ai raconté.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+maman|On t'a écouté.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6363,7 +6766,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Nino s'assoit à la table. Il écoute. Un mot le gêne. C'est un malaise. Le soir, il raconte à la maison.</t>
+          <t>Nino tire la chaise, tout doux. Le bois de la table est lisse, un peu froid. Un crayon a laissé une trace grise. Ça sent le bois et la craie. La maîtresse parle, près de la table. Nino écoute. Un mot le gêne, tout à coup. C'est un malaise. Le ventre se serre. J'ai un malaise. Tu as écouté. Si malaise, tu racontes à la maison. Je raconte à papa et maman. Bravo, Nino. On t'écoute, ce soir. La trace grise reste, sur le bois.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6499,10 +6902,29 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Nino s'assoit à la table. Il écoute. Un mot le gêne. C'est un malaise. Le soir, il raconte à la maison.</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr"/>
+          <t>narrateur|Nino tire la chaise, tout doux.
+narrateur|Le bois de la table est lisse, un peu froid.
+narrateur|Un crayon a laissé une trace grise.
+narrateur|Ça sent le bois et la craie.
+narrateur|La maîtresse parle, près de la table.
+narrateur|Nino écoute.
+narrateur|Un mot le gêne, tout à coup.
+narrateur|C'est un malaise.
+narrateur|Le ventre se serre.
+enfant-m|J'ai un malaise.
+maman|Tu as écouté.
+papa|Si malaise, tu racontes à la maison.
+enfant-m|Je raconte à papa et maman.
+maman|Bravo, Nino.
+maman|On t'écoute, ce soir.
+narrateur|La trace grise reste, sur le bois.</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>chaise</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6683,7 +7105,8 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|À la table, Nino a un malaise. Que fait-il ?</t>
+          <t>narrateur|À la table, Nino a un malaise.
+maman|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6711,7 +7134,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Écouter. Si malaise, raconter à la maison.</t>
+          <t>Oui. On écoute la maîtresse. Si malaise, raconter à la maison. Nino respire, tout calme. Bravo, Nino. Tu as fait du bon travail. Je raconte à la maison.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6855,7 +7278,13 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Écouter. Si malaise, raconter à la maison.</t>
+          <t>narrateur|Oui.
+maman|On écoute la maîtresse.
+papa|Si malaise, raconter à la maison.
+narrateur|Nino respire, tout calme.
+maman|Bravo, Nino.
+maman|Tu as fait du bon travail.
+enfant-m|Je raconte à la maison.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6883,7 +7312,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre l'histoire, le dessin, ou la chanson.</t>
+          <t>La classe continue, tout doux. L'histoire, le dessin, ou la chanson ? On prend ça. Puis on raconte.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7055,7 +7484,10 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre l'histoire, le dessin, ou la chanson.</t>
+          <t>narrateur|La classe continue, tout doux.
+maman|L'histoire, le dessin, ou la chanson ?
+papa|On prend ça.
+papa|Puis on raconte.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7083,7 +7515,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>À la table, l'histoire. Nino écoute. Malaise. Il va raconter à la maison.</t>
+          <t>À la table, le livre est ouvert. Une image montre un bateau bleu. Nino écoute l'histoire, les pieds par terre. Un mot le gêne. C'est un malaise. Je raconterai à maman. À papa. Plus tard, maman prend sa main. Tu as écouté, à la table ? Oui. J'ai un malaise. Tu viens le dire à la maison. Bravo, Nino. C'est du bon travail. Le bateau bleu reste sur la page.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7223,10 +7655,28 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|À la table, l'histoire. Nino écoute. Malaise. Il va raconter à la maison.</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr"/>
+          <t>narrateur|À la table, le livre est ouvert.
+narrateur|Une image montre un bateau bleu.
+narrateur|Nino écoute l'histoire, les pieds par terre.
+narrateur|Un mot le gêne.
+narrateur|C'est un malaise.
+enfant-m|Je raconterai à maman.
+enfant-m|À papa.
+narrateur|Plus tard, maman prend sa main.
+maman|Tu as écouté, à la table ?
+enfant-m|Oui.
+enfant-m|J'ai un malaise.
+papa|Tu viens le dire à la maison.
+maman|Bravo, Nino.
+maman|C'est du bon travail.
+narrateur|Le bateau bleu reste sur la page.</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7251,7 +7701,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre maman, papa, ou la sœur.</t>
+          <t>Le soir, Nino raconte à quelqu'un. Maman, papa, ou Sarah ? Choisis. On t'écoute.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7415,7 +7865,10 @@
       <c r="AV37" s="2" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+          <t>narrateur|Le soir, Nino raconte à quelqu'un.
+maman|Maman, papa, ou Sarah ?
+papa|Choisis.
+papa|On t'écoute.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7443,7 +7896,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Nino rejoint maman. Il a écouté à la table, pendant l'histoire. Il a eu un malaise. Il vient raconter à la maison.</t>
+          <t>Le soir, la maison sent la soupe. La lampe fait un rond jaune. Nino rejoint maman, près de la casserole. Il a écouté à la table, pendant l'histoire. Maman, j'ai un malaise. Un camarade a parlé tout bas. Tu as bien fait de raconter. Tu as écouté la maîtresse. Si tu as un malaise, tu viens nous le dire. Je raconte à la maison. Bravo, Nino. C'est du bon travail. Je t'écoute. On reste un moment. Le bois de la table sent encore l'école. Le ventre de Nino se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7583,10 +8036,29 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Nino rejoint maman. Il a écouté à la table, pendant l'histoire. Il a eu un malaise. Il vient raconter à la maison.</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr"/>
+          <t>narrateur|Le soir, la maison sent la soupe.
+narrateur|La lampe fait un rond jaune.
+narrateur|Nino rejoint maman, près de la casserole.
+narrateur|Il a écouté à la table, pendant l'histoire.
+enfant-m|Maman, j'ai un malaise.
+enfant-m|Un camarade a parlé tout bas.
+maman|Tu as bien fait de raconter.
+maman|Tu as écouté la maîtresse.
+papa|Si tu as un malaise, tu viens nous le dire.
+enfant-m|Je raconte à la maison.
+maman|Bravo, Nino.
+maman|C'est du bon travail.
+papa|Je t'écoute.
+papa|On reste un moment.
+narrateur|Le bois de la table sent encore l'école.
+narrateur|Le ventre de Nino se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>soupe</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7611,7 +8083,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nino a écouté à la table, pendant l'histoire. Puis il a raconté, à maman. Le bois lisse de la table reste dans sa tête. Le livre jaune est fermé, tout calme. Maman pose la main sur son épaule. J'ai écouté. Puis j'ai raconté. Bravo, Nino. Tu as fait du bon travail. On t'a écouté. Si malaise, tu reviens nous le dire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7751,7 +8223,18 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nino a écouté à la table, pendant l'histoire.
+narrateur|Puis il a raconté, à maman.
+narrateur|Le bois lisse de la table reste dans sa tête.
+narrateur|Le livre jaune est fermé, tout calme.
+narrateur|Maman pose la main sur son épaule.
+enfant-m|J'ai écouté.
+enfant-m|Puis j'ai raconté.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+maman|On t'a écouté.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7779,7 +8262,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Nino rejoint papa. Il a écouté à la table, pendant l'histoire. Il a eu un malaise. Il vient raconter à la maison.</t>
+          <t>Le soir, la maison sent la soupe. La lampe fait un rond jaune. Nino rejoint papa, près du cacao. Il a écouté à la table, pendant l'histoire. Papa, j'ai un malaise. Un mot m'a gêné, à l'école. Tu as bien fait de le dire. Tu as écouté la maîtresse. Si malaise, tu racontes à la maison. Je raconte à papa et maman. Bravo, Nino. Tu as fait du bon travail. On t'écoute. Ton ventre peut se desserrer. Papa aligne trois miettes, comme des mots. Le ventre de Nino se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7919,10 +8402,29 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Nino rejoint papa. Il a écouté à la table, pendant l'histoire. Il a eu un malaise. Il vient raconter à la maison.</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr"/>
+          <t>narrateur|Le soir, la maison sent la soupe.
+narrateur|La lampe fait un rond jaune.
+narrateur|Nino rejoint papa, près du cacao.
+narrateur|Il a écouté à la table, pendant l'histoire.
+enfant-m|Papa, j'ai un malaise.
+enfant-m|Un mot m'a gêné, à l'école.
+papa|Tu as bien fait de le dire.
+papa|Tu as écouté la maîtresse.
+maman|Si malaise, tu racontes à la maison.
+enfant-m|Je raconte à papa et maman.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+maman|On t'écoute.
+maman|Ton ventre peut se desserrer.
+narrateur|Papa aligne trois miettes, comme des mots.
+narrateur|Le ventre de Nino se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>cacao</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7947,7 +8449,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nino a écouté à la table, pendant l'histoire. Puis il a raconté, à papa. Le bois lisse de la table reste dans sa tête. Le livre jaune est fermé, tout calme. Papa souffle sur le cacao, tout doux. J'ai écouté. Puis j'ai raconté. Bravo, Nino. Tu as fait du bon travail. On t'a écouté. Si malaise, tu reviens nous le dire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8087,7 +8589,18 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nino a écouté à la table, pendant l'histoire.
+narrateur|Puis il a raconté, à papa.
+narrateur|Le bois lisse de la table reste dans sa tête.
+narrateur|Le livre jaune est fermé, tout calme.
+narrateur|Papa souffle sur le cacao, tout doux.
+enfant-m|J'ai écouté.
+enfant-m|Puis j'ai raconté.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+maman|On t'a écouté.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8115,7 +8628,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Nino rejoint la sœur. Il a écouté à la table, pendant l'histoire. Il a eu un malaise. Il vient raconter à la maison.</t>
+          <t>Le soir, la maison sent la soupe. La lampe fait un rond jaune. Nino rejoint Sarah, près du bol de Sarah. Il a écouté à la table, pendant l'histoire. Sarah, j'ai un malaise. Je t'écoute, Nino. Un camarade a chuchoté. Nino veut raconter. Tu as écouté la maîtresse. Si malaise, raconter à la maison. Je raconte à la maison. Bravo, les enfants. C'est du bon travail. Sarah écoute, les deux mains autour du bol. Le ventre de Nino se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8255,10 +8768,28 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Nino rejoint la sœur. Il a écouté à la table, pendant l'histoire. Il a eu un malaise. Il vient raconter à la maison.</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr"/>
+          <t>narrateur|Le soir, la maison sent la soupe.
+narrateur|La lampe fait un rond jaune.
+narrateur|Nino rejoint Sarah, près du bol de Sarah.
+narrateur|Il a écouté à la table, pendant l'histoire.
+enfant-m|Sarah, j'ai un malaise.
+enfant-f|Je t'écoute, Nino.
+enfant-m|Un camarade a chuchoté.
+enfant-f|Nino veut raconter.
+maman|Tu as écouté la maîtresse.
+papa|Si malaise, raconter à la maison.
+enfant-m|Je raconte à la maison.
+maman|Bravo, les enfants.
+maman|C'est du bon travail.
+narrateur|Sarah écoute, les deux mains autour du bol.
+narrateur|Le ventre de Nino se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>bol</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8283,7 +8814,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nino a écouté à la table, pendant l'histoire. Puis il a raconté, à Sarah. Le bois lisse de la table reste dans sa tête. Le livre jaune est fermé, tout calme. Sarah pousse son bol vers Nino. J'ai écouté. Puis j'ai raconté. Bravo, Nino. Tu as fait du bon travail. On t'a écouté. Si malaise, tu reviens nous le dire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8423,7 +8954,18 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nino a écouté à la table, pendant l'histoire.
+narrateur|Puis il a raconté, à Sarah.
+narrateur|Le bois lisse de la table reste dans sa tête.
+narrateur|Le livre jaune est fermé, tout calme.
+narrateur|Sarah pousse son bol vers Nino.
+enfant-m|J'ai écouté.
+enfant-m|Puis j'ai raconté.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+maman|On t'a écouté.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8451,7 +8993,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Le dessin est posé. Nino écoute. Un malaise. Raconter à la maison.</t>
+          <t>À la table, le dessin est posé. Le papier est un peu rêche. Nino écoute. Il tient le crayon. Un camarade chuchote. Le ventre se serre. J'ai un malaise. Je raconte à la maison. Plus tard, papa est près des casiers. Tu as tes crayons, Nino ? Oui. J'ai un malaise, papa. Tu as écouté. On t'écoute, ce soir. Tu as bien fait de nous le dire. Une mine rouge tache le bout du doigt.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8591,10 +9133,29 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Le dessin est posé. Nino écoute. Un malaise. Raconter à la maison.</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr"/>
+          <t>narrateur|À la table, le dessin est posé.
+narrateur|Le papier est un peu rêche.
+narrateur|Nino écoute.
+narrateur|Il tient le crayon.
+narrateur|Un camarade chuchote.
+narrateur|Le ventre se serre.
+enfant-m|J'ai un malaise.
+enfant-m|Je raconte à la maison.
+narrateur|Plus tard, papa est près des casiers.
+papa|Tu as tes crayons, Nino ?
+enfant-m|Oui.
+enfant-m|J'ai un malaise, papa.
+maman|Tu as écouté.
+maman|On t'écoute, ce soir.
+papa|Tu as bien fait de nous le dire.
+narrateur|Une mine rouge tache le bout du doigt.</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>crayon</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8619,7 +9180,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre maman, papa, ou la sœur.</t>
+          <t>Le soir, Nino raconte à quelqu'un. Maman, papa, ou Sarah ? Choisis. On t'écoute.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8783,7 +9344,10 @@
       <c r="AV45" s="2" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+          <t>narrateur|Le soir, Nino raconte à quelqu'un.
+maman|Maman, papa, ou Sarah ?
+papa|Choisis.
+papa|On t'écoute.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8811,7 +9375,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Nino rejoint maman. Il a écouté à la table, pendant le dessin. Il a eu un malaise. Il vient raconter à la maison.</t>
+          <t>Le soir, la maison sent la soupe. La lampe fait un rond jaune. Nino rejoint maman, près de la casserole. Il a écouté à la table, pendant le dessin. Maman, j'ai un malaise. Un camarade a parlé tout bas. Tu as bien fait de raconter. Tu as écouté la maîtresse. Si tu as un malaise, tu viens nous le dire. Je raconte à la maison. Bravo, Nino. C'est du bon travail. Je t'écoute. On reste un moment. Maman range un crayon, près du sel. Le ventre de Nino se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8951,10 +9515,29 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Nino rejoint maman. Il a écouté à la table, pendant le dessin. Il a eu un malaise. Il vient raconter à la maison.</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr"/>
+          <t>narrateur|Le soir, la maison sent la soupe.
+narrateur|La lampe fait un rond jaune.
+narrateur|Nino rejoint maman, près de la casserole.
+narrateur|Il a écouté à la table, pendant le dessin.
+enfant-m|Maman, j'ai un malaise.
+enfant-m|Un camarade a parlé tout bas.
+maman|Tu as bien fait de raconter.
+maman|Tu as écouté la maîtresse.
+papa|Si tu as un malaise, tu viens nous le dire.
+enfant-m|Je raconte à la maison.
+maman|Bravo, Nino.
+maman|C'est du bon travail.
+papa|Je t'écoute.
+papa|On reste un moment.
+narrateur|Maman range un crayon, près du sel.
+narrateur|Le ventre de Nino se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>soupe</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8979,7 +9562,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nino a écouté à la table, pendant le dessin. Puis il a raconté, à maman. Le bois lisse de la table reste dans sa tête. Le crayon rouge repose, tout calme. Maman pose la main sur son épaule. J'ai écouté. Puis j'ai raconté. Bravo, Nino. Tu as fait du bon travail. On t'a écouté. Si malaise, tu reviens nous le dire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9119,7 +9702,18 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nino a écouté à la table, pendant le dessin.
+narrateur|Puis il a raconté, à maman.
+narrateur|Le bois lisse de la table reste dans sa tête.
+narrateur|Le crayon rouge repose, tout calme.
+narrateur|Maman pose la main sur son épaule.
+enfant-m|J'ai écouté.
+enfant-m|Puis j'ai raconté.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+maman|On t'a écouté.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9147,7 +9741,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Nino rejoint papa. Il a écouté à la table, pendant le dessin. Il a eu un malaise. Il vient raconter à la maison.</t>
+          <t>Le soir, la maison sent la soupe. La lampe fait un rond jaune. Nino rejoint papa, près du cacao. Il a écouté à la table, pendant le dessin. Papa, j'ai un malaise. Un mot m'a gêné, à l'école. Tu as bien fait de le dire. Tu as écouté la maîtresse. Si malaise, tu racontes à la maison. Je raconte à papa et maman. Bravo, Nino. Tu as fait du bon travail. On t'écoute. Ton ventre peut se desserrer. Papa souffle une mine, sur la nappe. Le ventre de Nino se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9287,10 +9881,29 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Nino rejoint papa. Il a écouté à la table, pendant le dessin. Il a eu un malaise. Il vient raconter à la maison.</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr"/>
+          <t>narrateur|Le soir, la maison sent la soupe.
+narrateur|La lampe fait un rond jaune.
+narrateur|Nino rejoint papa, près du cacao.
+narrateur|Il a écouté à la table, pendant le dessin.
+enfant-m|Papa, j'ai un malaise.
+enfant-m|Un mot m'a gêné, à l'école.
+papa|Tu as bien fait de le dire.
+papa|Tu as écouté la maîtresse.
+maman|Si malaise, tu racontes à la maison.
+enfant-m|Je raconte à papa et maman.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+maman|On t'écoute.
+maman|Ton ventre peut se desserrer.
+narrateur|Papa souffle une mine, sur la nappe.
+narrateur|Le ventre de Nino se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>cacao</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9315,7 +9928,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nino a écouté à la table, pendant le dessin. Puis il a raconté, à papa. Le bois lisse de la table reste dans sa tête. Le crayon rouge repose, tout calme. Papa souffle sur le cacao, tout doux. J'ai écouté. Puis j'ai raconté. Bravo, Nino. Tu as fait du bon travail. On t'a écouté. Si malaise, tu reviens nous le dire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9455,7 +10068,18 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nino a écouté à la table, pendant le dessin.
+narrateur|Puis il a raconté, à papa.
+narrateur|Le bois lisse de la table reste dans sa tête.
+narrateur|Le crayon rouge repose, tout calme.
+narrateur|Papa souffle sur le cacao, tout doux.
+enfant-m|J'ai écouté.
+enfant-m|Puis j'ai raconté.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+maman|On t'a écouté.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9483,7 +10107,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Nino rejoint la sœur. Il a écouté à la table, pendant le dessin. Il a eu un malaise. Il vient raconter à la maison.</t>
+          <t>Le soir, la maison sent la soupe. La lampe fait un rond jaune. Nino rejoint Sarah, près du bol de Sarah. Il a écouté à la table, pendant le dessin. Sarah, j'ai un malaise. Je t'écoute, Nino. Un camarade a chuchoté. Nino veut raconter. Tu as écouté la maîtresse. Si malaise, raconter à la maison. Je raconte à la maison. Bravo, les enfants. C'est du bon travail. Sarah pose son ours, pour écouter mieux. Le ventre de Nino se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9623,10 +10247,28 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Nino rejoint la sœur. Il a écouté à la table, pendant le dessin. Il a eu un malaise. Il vient raconter à la maison.</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr"/>
+          <t>narrateur|Le soir, la maison sent la soupe.
+narrateur|La lampe fait un rond jaune.
+narrateur|Nino rejoint Sarah, près du bol de Sarah.
+narrateur|Il a écouté à la table, pendant le dessin.
+enfant-m|Sarah, j'ai un malaise.
+enfant-f|Je t'écoute, Nino.
+enfant-m|Un camarade a chuchoté.
+enfant-f|Nino veut raconter.
+maman|Tu as écouté la maîtresse.
+papa|Si malaise, raconter à la maison.
+enfant-m|Je raconte à la maison.
+maman|Bravo, les enfants.
+maman|C'est du bon travail.
+narrateur|Sarah pose son ours, pour écouter mieux.
+narrateur|Le ventre de Nino se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>bol</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9651,7 +10293,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nino a écouté à la table, pendant le dessin. Puis il a raconté, à Sarah. Le bois lisse de la table reste dans sa tête. Le crayon rouge repose, tout calme. Sarah pousse son bol vers Nino. J'ai écouté. Puis j'ai raconté. Bravo, Nino. Tu as fait du bon travail. On t'a écouté. Si malaise, tu reviens nous le dire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9791,7 +10433,18 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nino a écouté à la table, pendant le dessin.
+narrateur|Puis il a raconté, à Sarah.
+narrateur|Le bois lisse de la table reste dans sa tête.
+narrateur|Le crayon rouge repose, tout calme.
+narrateur|Sarah pousse son bol vers Nino.
+enfant-m|J'ai écouté.
+enfant-m|Puis j'ai raconté.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+maman|On t'a écouté.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9819,7 +10472,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>On chante à la table. Nino écoute. Malaise. Il raconte à la maison.</t>
+          <t>À la table, on chante tout bas. Un verre d'eau tremble un peu. Nino écoute la chanson. Son ventre se serre. C'est un malaise. Je le dirai à la maison. Plus tard, maman l'attend près du radiateur. Tes bottes ont séché, Nino. Maman, j'ai un malaise. Tu as écouté la maîtresse. Ce soir, tu racontes. On est là. Le verre d'eau ne tremble plus.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9955,10 +10608,26 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|On chante à la table. Nino écoute. Malaise. Il raconte à la maison.</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr"/>
+          <t>narrateur|À la table, on chante tout bas.
+narrateur|Un verre d'eau tremble un peu.
+narrateur|Nino écoute la chanson.
+narrateur|Son ventre se serre.
+narrateur|C'est un malaise.
+enfant-m|Je le dirai à la maison.
+narrateur|Plus tard, maman l'attend près du radiateur.
+maman|Tes bottes ont séché, Nino.
+enfant-m|Maman, j'ai un malaise.
+papa|Tu as écouté la maîtresse.
+maman|Ce soir, tu racontes.
+maman|On est là.
+narrateur|Le verre d'eau ne tremble plus.</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>voix_enfant</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9983,7 +10652,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre maman, papa, ou la sœur.</t>
+          <t>Le soir, Nino raconte à quelqu'un. Maman, papa, ou Sarah ? Choisis. On t'écoute.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10147,7 +10816,10 @@
       <c r="AV53" s="2" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+          <t>narrateur|Le soir, Nino raconte à quelqu'un.
+maman|Maman, papa, ou Sarah ?
+papa|Choisis.
+papa|On t'écoute.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10175,7 +10847,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Nino rejoint maman. Il a écouté à la table, pendant la chanson. Il a eu un malaise. Il vient raconter à la maison.</t>
+          <t>Le soir, la maison sent la soupe. La lampe fait un rond jaune. Nino rejoint maman, près de la casserole. Il a écouté à la table, pendant la chanson. Maman, j'ai un malaise. Un camarade a parlé tout bas. Tu as bien fait de raconter. Tu as écouté la maîtresse. Si tu as un malaise, tu viens nous le dire. Je raconte à la maison. Bravo, Nino. C'est du bon travail. Je t'écoute. On reste un moment. La casserole chante, plus fort que la peur. Le ventre de Nino se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10315,10 +10987,29 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Nino rejoint maman. Il a écouté à la table, pendant la chanson. Il a eu un malaise. Il vient raconter à la maison.</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr"/>
+          <t>narrateur|Le soir, la maison sent la soupe.
+narrateur|La lampe fait un rond jaune.
+narrateur|Nino rejoint maman, près de la casserole.
+narrateur|Il a écouté à la table, pendant la chanson.
+enfant-m|Maman, j'ai un malaise.
+enfant-m|Un camarade a parlé tout bas.
+maman|Tu as bien fait de raconter.
+maman|Tu as écouté la maîtresse.
+papa|Si tu as un malaise, tu viens nous le dire.
+enfant-m|Je raconte à la maison.
+maman|Bravo, Nino.
+maman|C'est du bon travail.
+papa|Je t'écoute.
+papa|On reste un moment.
+narrateur|La casserole chante, plus fort que la peur.
+narrateur|Le ventre de Nino se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>soupe</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10343,7 +11034,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nino a écouté à la table, pendant la chanson. Puis il a raconté, à maman. Le bois lisse de la table reste dans sa tête. La chanson s'est tue, tout doux. Maman pose la main sur son épaule. J'ai écouté. Puis j'ai raconté. Bravo, Nino. Tu as fait du bon travail. On t'a écouté. Si malaise, tu reviens nous le dire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10483,7 +11174,18 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nino a écouté à la table, pendant la chanson.
+narrateur|Puis il a raconté, à maman.
+narrateur|Le bois lisse de la table reste dans sa tête.
+narrateur|La chanson s'est tue, tout doux.
+narrateur|Maman pose la main sur son épaule.
+enfant-m|J'ai écouté.
+enfant-m|Puis j'ai raconté.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+maman|On t'a écouté.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10511,7 +11213,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Nino rejoint papa. Il a écouté à la table, pendant la chanson. Il a eu un malaise. Il vient raconter à la maison.</t>
+          <t>Le soir, la maison sent la soupe. La lampe fait un rond jaune. Nino rejoint papa, près du cacao. Il a écouté à la table, pendant la chanson. Papa, j'ai un malaise. Un mot m'a gêné, à l'école. Tu as bien fait de le dire. Tu as écouté la maîtresse. Si malaise, tu racontes à la maison. Je raconte à papa et maman. Bravo, Nino. Tu as fait du bon travail. On t'écoute. Ton ventre peut se desserrer. Papa tapote le bord du bol, tout léger. Le ventre de Nino se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10651,10 +11353,29 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Nino rejoint papa. Il a écouté à la table, pendant la chanson. Il a eu un malaise. Il vient raconter à la maison.</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr"/>
+          <t>narrateur|Le soir, la maison sent la soupe.
+narrateur|La lampe fait un rond jaune.
+narrateur|Nino rejoint papa, près du cacao.
+narrateur|Il a écouté à la table, pendant la chanson.
+enfant-m|Papa, j'ai un malaise.
+enfant-m|Un mot m'a gêné, à l'école.
+papa|Tu as bien fait de le dire.
+papa|Tu as écouté la maîtresse.
+maman|Si malaise, tu racontes à la maison.
+enfant-m|Je raconte à papa et maman.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+maman|On t'écoute.
+maman|Ton ventre peut se desserrer.
+narrateur|Papa tapote le bord du bol, tout léger.
+narrateur|Le ventre de Nino se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>cacao</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10679,7 +11400,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nino a écouté à la table, pendant la chanson. Puis il a raconté, à papa. Le bois lisse de la table reste dans sa tête. La chanson s'est tue, tout doux. Papa souffle sur le cacao, tout doux. J'ai écouté. Puis j'ai raconté. Bravo, Nino. Tu as fait du bon travail. On t'a écouté. Si malaise, tu reviens nous le dire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10819,7 +11540,18 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nino a écouté à la table, pendant la chanson.
+narrateur|Puis il a raconté, à papa.
+narrateur|Le bois lisse de la table reste dans sa tête.
+narrateur|La chanson s'est tue, tout doux.
+narrateur|Papa souffle sur le cacao, tout doux.
+enfant-m|J'ai écouté.
+enfant-m|Puis j'ai raconté.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+maman|On t'a écouté.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10847,7 +11579,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Nino rejoint la sœur. Il a écouté à la table, pendant la chanson. Il a eu un malaise. Il vient raconter à la maison.</t>
+          <t>Le soir, la maison sent la soupe. La lampe fait un rond jaune. Nino rejoint Sarah, près du bol de Sarah. Il a écouté à la table, pendant la chanson. Sarah, j'ai un malaise. Je t'écoute, Nino. Un camarade a chuchoté. Nino veut raconter. Tu as écouté la maîtresse. Si malaise, raconter à la maison. Je raconte à la maison. Bravo, les enfants. C'est du bon travail. Sarah rit un peu, puis elle se tait. Le ventre de Nino se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -10987,10 +11719,28 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Nino rejoint la sœur. Il a écouté à la table, pendant la chanson. Il a eu un malaise. Il vient raconter à la maison.</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr"/>
+          <t>narrateur|Le soir, la maison sent la soupe.
+narrateur|La lampe fait un rond jaune.
+narrateur|Nino rejoint Sarah, près du bol de Sarah.
+narrateur|Il a écouté à la table, pendant la chanson.
+enfant-m|Sarah, j'ai un malaise.
+enfant-f|Je t'écoute, Nino.
+enfant-m|Un camarade a chuchoté.
+enfant-f|Nino veut raconter.
+maman|Tu as écouté la maîtresse.
+papa|Si malaise, raconter à la maison.
+enfant-m|Je raconte à la maison.
+maman|Bravo, les enfants.
+maman|C'est du bon travail.
+narrateur|Sarah rit un peu, puis elle se tait.
+narrateur|Le ventre de Nino se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>bol</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11015,7 +11765,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nino a écouté à la table, pendant la chanson. Puis il a raconté, à Sarah. Le bois lisse de la table reste dans sa tête. La chanson s'est tue, tout doux. Sarah pousse son bol vers Nino. J'ai écouté. Puis j'ai raconté. Bravo, Nino. Tu as fait du bon travail. On t'a écouté. Si malaise, tu reviens nous le dire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11155,7 +11905,18 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nino a écouté à la table, pendant la chanson.
+narrateur|Puis il a raconté, à Sarah.
+narrateur|Le bois lisse de la table reste dans sa tête.
+narrateur|La chanson s'est tue, tout doux.
+narrateur|Sarah pousse son bol vers Nino.
+enfant-m|J'ai écouté.
+enfant-m|Puis j'ai raconté.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+maman|On t'a écouté.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11183,7 +11944,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Nino est au préau. Il écoute la maîtresse. Son ventre se serre. Un malaise. Il racontera à la maison.</t>
+          <t>Nino pousse la porte du préau. Le sol est frais, encore un peu humide. Une goutte tombe d'un rebord. Ça sent la pluie et le ciment. La voix de la maîtresse sonne, un peu forte. Nino écoute quand même. Un camarade parle tout bas, près de lui. Le ventre se serre. Un malaise. Mon ventre est serré. C'est un malaise. Tu as écouté la maîtresse. Ce soir, tu racontes à la maison. Je raconte à la maison. Bravo, Nino. Tu as parlé. La goutte fait un petit rond sombre.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11323,10 +12084,30 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Nino est au préau. Il écoute la maîtresse. Son ventre se serre. Un malaise. Il racontera à la maison.</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr"/>
+          <t>narrateur|Nino pousse la porte du préau.
+narrateur|Le sol est frais, encore un peu humide.
+narrateur|Une goutte tombe d'un rebord.
+narrateur|Ça sent la pluie et le ciment.
+narrateur|La voix de la maîtresse sonne, un peu forte.
+narrateur|Nino écoute quand même.
+narrateur|Un camarade parle tout bas, près de lui.
+narrateur|Le ventre se serre.
+narrateur|Un malaise.
+enfant-m|Mon ventre est serré.
+maman|C'est un malaise.
+maman|Tu as écouté la maîtresse.
+papa|Ce soir, tu racontes à la maison.
+enfant-m|Je raconte à la maison.
+maman|Bravo, Nino.
+maman|Tu as parlé.
+narrateur|La goutte fait un petit rond sombre.</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>goutte</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11351,7 +12132,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Au préau, Nino a un malaise. Que fait-il ?</t>
+          <t>Sous le préau, Nino a un malaise. Que fait-il ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11507,7 +12288,8 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|Au préau, Nino a un malaise. Que fait-il ?</t>
+          <t>narrateur|Sous le préau, Nino a un malaise.
+maman|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11535,7 +12317,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Nino a su écouter. Il saura raconter à la maison.</t>
+          <t>Oui. On écoute la maîtresse. Si malaise, raconter à la maison. Nino respire, tout calme. Bravo, Nino. Tu as fait du bon travail. Je raconte à la maison.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11679,7 +12461,13 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Nino a su écouter. Il saura raconter à la maison.</t>
+          <t>narrateur|Oui.
+maman|On écoute la maîtresse.
+papa|Si malaise, raconter à la maison.
+narrateur|Nino respire, tout calme.
+maman|Bravo, Nino.
+maman|Tu as fait du bon travail.
+enfant-m|Je raconte à la maison.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11707,7 +12495,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre l'histoire, le dessin, ou la chanson.</t>
+          <t>La classe continue, tout doux. L'histoire, le dessin, ou la chanson ? On prend ça. Puis on raconte.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11879,7 +12667,10 @@
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre l'histoire, le dessin, ou la chanson.</t>
+          <t>narrateur|La classe continue, tout doux.
+maman|L'histoire, le dessin, ou la chanson ?
+papa|On prend ça.
+papa|Puis on raconte.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11907,7 +12698,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Au préau, l'histoire. Nino écoute. Malaise. Raconter à la maison.</t>
+          <t>Sous le préau, l'histoire commence. Le livre claque un peu, au vent. Nino écoute, les mains dans les poches. Un mot le gêne. C'est un malaise. Je raconte à la maison. Plus tard, papa arrive, le bonnet à la main. Sarah l'a oublié. Et toi ? J'ai un malaise, papa. Tu as écouté. Tu nous le diras. On rentre. On t'écoute. Une goutte tombe encore, du rebord.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12047,10 +12838,28 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Au préau, l'histoire. Nino écoute. Malaise. Raconter à la maison.</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr"/>
+          <t>narrateur|Sous le préau, l'histoire commence.
+narrateur|Le livre claque un peu, au vent.
+narrateur|Nino écoute, les mains dans les poches.
+narrateur|Un mot le gêne.
+narrateur|C'est un malaise.
+enfant-m|Je raconte à la maison.
+narrateur|Plus tard, papa arrive, le bonnet à la main.
+papa|Sarah l'a oublié.
+papa|Et toi ?
+enfant-m|J'ai un malaise, papa.
+maman|Tu as écouté.
+maman|Tu nous le diras.
+papa|On rentre.
+papa|On t'écoute.
+narrateur|Une goutte tombe encore, du rebord.</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12075,7 +12884,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre maman, papa, ou la sœur.</t>
+          <t>Le soir, Nino raconte à quelqu'un. Maman, papa, ou Sarah ? Choisis. On t'écoute.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12239,7 +13048,10 @@
       <c r="AV65" s="2" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+          <t>narrateur|Le soir, Nino raconte à quelqu'un.
+maman|Maman, papa, ou Sarah ?
+papa|Choisis.
+papa|On t'écoute.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12267,7 +13079,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Nino rejoint maman. Il a écouté à le préau, pendant l'histoire. Il a eu un malaise. Il vient raconter à la maison.</t>
+          <t>Le soir, la maison sent la soupe. La lampe fait un rond jaune. Nino rejoint maman, près de la casserole. Il a écouté sous le préau, pendant l'histoire. Maman, j'ai un malaise. Un camarade a parlé tout bas. Tu as bien fait de raconter. Tu as écouté la maîtresse. Si tu as un malaise, tu viens nous le dire. Je raconte à la maison. Bravo, Nino. C'est du bon travail. Je t'écoute. On reste un moment. Une odeur de pluie reste dans les cheveux. Le ventre de Nino se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12407,10 +13219,29 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Nino rejoint maman. Il a écouté à le préau, pendant l'histoire. Il a eu un malaise. Il vient raconter à la maison.</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr"/>
+          <t>narrateur|Le soir, la maison sent la soupe.
+narrateur|La lampe fait un rond jaune.
+narrateur|Nino rejoint maman, près de la casserole.
+narrateur|Il a écouté sous le préau, pendant l'histoire.
+enfant-m|Maman, j'ai un malaise.
+enfant-m|Un camarade a parlé tout bas.
+maman|Tu as bien fait de raconter.
+maman|Tu as écouté la maîtresse.
+papa|Si tu as un malaise, tu viens nous le dire.
+enfant-m|Je raconte à la maison.
+maman|Bravo, Nino.
+maman|C'est du bon travail.
+papa|Je t'écoute.
+papa|On reste un moment.
+narrateur|Une odeur de pluie reste dans les cheveux.
+narrateur|Le ventre de Nino se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>soupe</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12435,7 +13266,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nino a écouté sous le préau, pendant l'histoire. Puis il a raconté, à maman. Une goutte du préau brille encore. Le livre jaune est fermé, tout calme. Maman pose la main sur son épaule. J'ai écouté. Puis j'ai raconté. Bravo, Nino. Tu as fait du bon travail. On t'a écouté. Si malaise, tu reviens nous le dire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12575,7 +13406,18 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nino a écouté sous le préau, pendant l'histoire.
+narrateur|Puis il a raconté, à maman.
+narrateur|Une goutte du préau brille encore.
+narrateur|Le livre jaune est fermé, tout calme.
+narrateur|Maman pose la main sur son épaule.
+enfant-m|J'ai écouté.
+enfant-m|Puis j'ai raconté.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+maman|On t'a écouté.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12603,7 +13445,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Nino rejoint papa. Il a écouté à le préau, pendant l'histoire. Il a eu un malaise. Il vient raconter à la maison.</t>
+          <t>Le soir, la maison sent la soupe. La lampe fait un rond jaune. Nino rejoint papa, près du cacao. Il a écouté sous le préau, pendant l'histoire. Papa, j'ai un malaise. Un mot m'a gêné, à l'école. Tu as bien fait de le dire. Tu as écouté la maîtresse. Si malaise, tu racontes à la maison. Je raconte à papa et maman. Bravo, Nino. Tu as fait du bon travail. On t'écoute. Ton ventre peut se desserrer. Papa pose le bonnet rouge, près du cacao. Le ventre de Nino se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12743,10 +13585,29 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Nino rejoint papa. Il a écouté à le préau, pendant l'histoire. Il a eu un malaise. Il vient raconter à la maison.</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr"/>
+          <t>narrateur|Le soir, la maison sent la soupe.
+narrateur|La lampe fait un rond jaune.
+narrateur|Nino rejoint papa, près du cacao.
+narrateur|Il a écouté sous le préau, pendant l'histoire.
+enfant-m|Papa, j'ai un malaise.
+enfant-m|Un mot m'a gêné, à l'école.
+papa|Tu as bien fait de le dire.
+papa|Tu as écouté la maîtresse.
+maman|Si malaise, tu racontes à la maison.
+enfant-m|Je raconte à papa et maman.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+maman|On t'écoute.
+maman|Ton ventre peut se desserrer.
+narrateur|Papa pose le bonnet rouge, près du cacao.
+narrateur|Le ventre de Nino se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>cacao</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12771,7 +13632,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nino a écouté sous le préau, pendant l'histoire. Puis il a raconté, à papa. Une goutte du préau brille encore. Le livre jaune est fermé, tout calme. Papa souffle sur le cacao, tout doux. J'ai écouté. Puis j'ai raconté. Bravo, Nino. Tu as fait du bon travail. On t'a écouté. Si malaise, tu reviens nous le dire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12911,7 +13772,18 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nino a écouté sous le préau, pendant l'histoire.
+narrateur|Puis il a raconté, à papa.
+narrateur|Une goutte du préau brille encore.
+narrateur|Le livre jaune est fermé, tout calme.
+narrateur|Papa souffle sur le cacao, tout doux.
+enfant-m|J'ai écouté.
+enfant-m|Puis j'ai raconté.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+maman|On t'a écouté.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12939,7 +13811,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Nino rejoint la sœur. Il a écouté à le préau, pendant l'histoire. Il a eu un malaise. Il vient raconter à la maison.</t>
+          <t>Le soir, la maison sent la soupe. La lampe fait un rond jaune. Nino rejoint Sarah, près du bol de Sarah. Il a écouté sous le préau, pendant l'histoire. Sarah, j'ai un malaise. Je t'écoute, Nino. Un camarade a chuchoté. Nino veut raconter. Tu as écouté la maîtresse. Si malaise, raconter à la maison. Je raconte à la maison. Bravo, les enfants. C'est du bon travail. Sarah remet le bonnet, tout de travers. Le ventre de Nino se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13079,10 +13951,28 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Nino rejoint la sœur. Il a écouté à le préau, pendant l'histoire. Il a eu un malaise. Il vient raconter à la maison.</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr"/>
+          <t>narrateur|Le soir, la maison sent la soupe.
+narrateur|La lampe fait un rond jaune.
+narrateur|Nino rejoint Sarah, près du bol de Sarah.
+narrateur|Il a écouté sous le préau, pendant l'histoire.
+enfant-m|Sarah, j'ai un malaise.
+enfant-f|Je t'écoute, Nino.
+enfant-m|Un camarade a chuchoté.
+enfant-f|Nino veut raconter.
+maman|Tu as écouté la maîtresse.
+papa|Si malaise, raconter à la maison.
+enfant-m|Je raconte à la maison.
+maman|Bravo, les enfants.
+maman|C'est du bon travail.
+narrateur|Sarah remet le bonnet, tout de travers.
+narrateur|Le ventre de Nino se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>bol</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13107,7 +13997,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nino a écouté sous le préau, pendant l'histoire. Puis il a raconté, à Sarah. Une goutte du préau brille encore. Le livre jaune est fermé, tout calme. Sarah pousse son bol vers Nino. J'ai écouté. Puis j'ai raconté. Bravo, Nino. Tu as fait du bon travail. On t'a écouté. Si malaise, tu reviens nous le dire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13247,7 +14137,18 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nino a écouté sous le préau, pendant l'histoire.
+narrateur|Puis il a raconté, à Sarah.
+narrateur|Une goutte du préau brille encore.
+narrateur|Le livre jaune est fermé, tout calme.
+narrateur|Sarah pousse son bol vers Nino.
+enfant-m|J'ai écouté.
+enfant-m|Puis j'ai raconté.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+maman|On t'a écouté.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13275,7 +14176,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Nino dessine au préau. Il écoute. Un malaise. Il racontera à la maison.</t>
+          <t>Sous le préau, Nino dessine. Le papier frémit. L'air est frais. Il écoute la consigne. Un camarade chuchote. C'est un malaise. Mon ventre se serre. Plus tard, maman s'essuie les mains. Tu as les joues froides, Nino. J'ai un malaise, maman. Tu as écouté. Tu racontes à la maison. Bravo. Viens. On rentre. Le dessin est un peu gondolé, à cause de l'air.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13415,10 +14316,29 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Nino dessine au préau. Il écoute. Un malaise. Il racontera à la maison.</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr"/>
+          <t>narrateur|Sous le préau, Nino dessine.
+narrateur|Le papier frémit.
+narrateur|L'air est frais.
+narrateur|Il écoute la consigne.
+narrateur|Un camarade chuchote.
+narrateur|C'est un malaise.
+enfant-m|Mon ventre se serre.
+narrateur|Plus tard, maman s'essuie les mains.
+maman|Tu as les joues froides, Nino.
+enfant-m|J'ai un malaise, maman.
+papa|Tu as écouté.
+papa|Tu racontes à la maison.
+maman|Bravo.
+maman|Viens.
+maman|On rentre.
+narrateur|Le dessin est un peu gondolé, à cause de l'air.</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>crayon</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13443,7 +14363,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre maman, papa, ou la sœur.</t>
+          <t>Le soir, Nino raconte à quelqu'un. Maman, papa, ou Sarah ? Choisis. On t'écoute.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13607,7 +14527,10 @@
       <c r="AV73" s="2" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+          <t>narrateur|Le soir, Nino raconte à quelqu'un.
+maman|Maman, papa, ou Sarah ?
+papa|Choisis.
+papa|On t'écoute.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13635,7 +14558,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Nino rejoint maman. Il a écouté à le préau, pendant le dessin. Il a eu un malaise. Il vient raconter à la maison.</t>
+          <t>Le soir, la maison sent la soupe. La lampe fait un rond jaune. Nino rejoint maman, près de la casserole. Il a écouté sous le préau, pendant le dessin. Maman, j'ai un malaise. Un camarade a parlé tout bas. Tu as bien fait de raconter. Tu as écouté la maîtresse. Si tu as un malaise, tu viens nous le dire. Je raconte à la maison. Bravo, Nino. C'est du bon travail. Je t'écoute. On reste un moment. Maman sèche une goutte, sur la joue. Le ventre de Nino se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13775,10 +14698,29 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Nino rejoint maman. Il a écouté à le préau, pendant le dessin. Il a eu un malaise. Il vient raconter à la maison.</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr"/>
+          <t>narrateur|Le soir, la maison sent la soupe.
+narrateur|La lampe fait un rond jaune.
+narrateur|Nino rejoint maman, près de la casserole.
+narrateur|Il a écouté sous le préau, pendant le dessin.
+enfant-m|Maman, j'ai un malaise.
+enfant-m|Un camarade a parlé tout bas.
+maman|Tu as bien fait de raconter.
+maman|Tu as écouté la maîtresse.
+papa|Si tu as un malaise, tu viens nous le dire.
+enfant-m|Je raconte à la maison.
+maman|Bravo, Nino.
+maman|C'est du bon travail.
+papa|Je t'écoute.
+papa|On reste un moment.
+narrateur|Maman sèche une goutte, sur la joue.
+narrateur|Le ventre de Nino se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>soupe</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13803,7 +14745,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nino a écouté sous le préau, pendant le dessin. Puis il a raconté, à maman. Une goutte du préau brille encore. Le crayon rouge repose, tout calme. Maman pose la main sur son épaule. J'ai écouté. Puis j'ai raconté. Bravo, Nino. Tu as fait du bon travail. On t'a écouté. Si malaise, tu reviens nous le dire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13943,7 +14885,18 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nino a écouté sous le préau, pendant le dessin.
+narrateur|Puis il a raconté, à maman.
+narrateur|Une goutte du préau brille encore.
+narrateur|Le crayon rouge repose, tout calme.
+narrateur|Maman pose la main sur son épaule.
+enfant-m|J'ai écouté.
+enfant-m|Puis j'ai raconté.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+maman|On t'a écouté.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -13971,7 +14924,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Nino rejoint papa. Il a écouté à le préau, pendant le dessin. Il a eu un malaise. Il vient raconter à la maison.</t>
+          <t>Le soir, la maison sent la soupe. La lampe fait un rond jaune. Nino rejoint papa, près du cacao. Il a écouté sous le préau, pendant le dessin. Papa, j'ai un malaise. Un mot m'a gêné, à l'école. Tu as bien fait de le dire. Tu as écouté la maîtresse. Si malaise, tu racontes à la maison. Je raconte à papa et maman. Bravo, Nino. Tu as fait du bon travail. On t'écoute. Ton ventre peut se desserrer. Papa ouvre la fenêtre. L'air est frais. Le ventre de Nino se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14111,10 +15064,30 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Nino rejoint papa. Il a écouté à le préau, pendant le dessin. Il a eu un malaise. Il vient raconter à la maison.</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr"/>
+          <t>narrateur|Le soir, la maison sent la soupe.
+narrateur|La lampe fait un rond jaune.
+narrateur|Nino rejoint papa, près du cacao.
+narrateur|Il a écouté sous le préau, pendant le dessin.
+enfant-m|Papa, j'ai un malaise.
+enfant-m|Un mot m'a gêné, à l'école.
+papa|Tu as bien fait de le dire.
+papa|Tu as écouté la maîtresse.
+maman|Si malaise, tu racontes à la maison.
+enfant-m|Je raconte à papa et maman.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+maman|On t'écoute.
+maman|Ton ventre peut se desserrer.
+narrateur|Papa ouvre la fenêtre.
+narrateur|L'air est frais.
+narrateur|Le ventre de Nino se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>cacao</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14139,7 +15112,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nino a écouté sous le préau, pendant le dessin. Puis il a raconté, à papa. Une goutte du préau brille encore. Le crayon rouge repose, tout calme. Papa souffle sur le cacao, tout doux. J'ai écouté. Puis j'ai raconté. Bravo, Nino. Tu as fait du bon travail. On t'a écouté. Si malaise, tu reviens nous le dire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14279,7 +15252,18 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nino a écouté sous le préau, pendant le dessin.
+narrateur|Puis il a raconté, à papa.
+narrateur|Une goutte du préau brille encore.
+narrateur|Le crayon rouge repose, tout calme.
+narrateur|Papa souffle sur le cacao, tout doux.
+enfant-m|J'ai écouté.
+enfant-m|Puis j'ai raconté.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+maman|On t'a écouté.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14307,7 +15291,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Nino rejoint la sœur. Il a écouté à le préau, pendant le dessin. Il a eu un malaise. Il vient raconter à la maison.</t>
+          <t>Le soir, la maison sent la soupe. La lampe fait un rond jaune. Nino rejoint Sarah, près du bol de Sarah. Il a écouté sous le préau, pendant le dessin. Sarah, j'ai un malaise. Je t'écoute, Nino. Un camarade a chuchoté. Nino veut raconter. Tu as écouté la maîtresse. Si malaise, raconter à la maison. Je raconte à la maison. Bravo, les enfants. C'est du bon travail. Sarah souffle sur une goutte, sur la table. Le ventre de Nino se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14447,10 +15431,28 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Nino rejoint la sœur. Il a écouté à le préau, pendant le dessin. Il a eu un malaise. Il vient raconter à la maison.</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr"/>
+          <t>narrateur|Le soir, la maison sent la soupe.
+narrateur|La lampe fait un rond jaune.
+narrateur|Nino rejoint Sarah, près du bol de Sarah.
+narrateur|Il a écouté sous le préau, pendant le dessin.
+enfant-m|Sarah, j'ai un malaise.
+enfant-f|Je t'écoute, Nino.
+enfant-m|Un camarade a chuchoté.
+enfant-f|Nino veut raconter.
+maman|Tu as écouté la maîtresse.
+papa|Si malaise, raconter à la maison.
+enfant-m|Je raconte à la maison.
+maman|Bravo, les enfants.
+maman|C'est du bon travail.
+narrateur|Sarah souffle sur une goutte, sur la table.
+narrateur|Le ventre de Nino se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>bol</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14475,7 +15477,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nino a écouté sous le préau, pendant le dessin. Puis il a raconté, à Sarah. Une goutte du préau brille encore. Le crayon rouge repose, tout calme. Sarah pousse son bol vers Nino. J'ai écouté. Puis j'ai raconté. Bravo, Nino. Tu as fait du bon travail. On t'a écouté. Si malaise, tu reviens nous le dire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14615,7 +15617,18 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nino a écouté sous le préau, pendant le dessin.
+narrateur|Puis il a raconté, à Sarah.
+narrateur|Une goutte du préau brille encore.
+narrateur|Le crayon rouge repose, tout calme.
+narrateur|Sarah pousse son bol vers Nino.
+enfant-m|J'ai écouté.
+enfant-m|Puis j'ai raconté.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+maman|On t'a écouté.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14643,7 +15656,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>La chanson au préau. Nino écoute. Malaise. Raconter à la maison.</t>
+          <t>Sous le préau, la chanson part. Elle tape contre les murs, tout clair. Nino écoute. Il chante un mot. Son ventre se serre. C'est un malaise. Je le dirai, ce soir. Plus tard, papa ouvre le caban. Le bouton jaune tient encore. Papa, j'ai un malaise. Tu as écouté. On t'écoute à la maison. Bravo, Nino. C'est du bon travail. La chanson s'arrête. Le préau redevient calme.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14783,10 +15796,29 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|La chanson au préau. Nino écoute. Malaise. Raconter à la maison.</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr"/>
+          <t>narrateur|Sous le préau, la chanson part.
+narrateur|Elle tape contre les murs, tout clair.
+narrateur|Nino écoute.
+narrateur|Il chante un mot.
+narrateur|Son ventre se serre.
+narrateur|C'est un malaise.
+enfant-m|Je le dirai, ce soir.
+narrateur|Plus tard, papa ouvre le caban.
+papa|Le bouton jaune tient encore.
+enfant-m|Papa, j'ai un malaise.
+maman|Tu as écouté.
+maman|On t'écoute à la maison.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La chanson s'arrête.
+narrateur|Le préau redevient calme.</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>voix_enfant</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14811,7 +15843,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre maman, papa, ou la sœur.</t>
+          <t>Le soir, Nino raconte à quelqu'un. Maman, papa, ou Sarah ? Choisis. On t'écoute.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -14975,7 +16007,10 @@
       <c r="AV81" s="2" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+          <t>narrateur|Le soir, Nino raconte à quelqu'un.
+maman|Maman, papa, ou Sarah ?
+papa|Choisis.
+papa|On t'écoute.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15003,7 +16038,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Nino rejoint maman. Il a écouté à le préau, pendant la chanson. Il a eu un malaise. Il vient raconter à la maison.</t>
+          <t>Le soir, la maison sent la soupe. La lampe fait un rond jaune. Nino rejoint maman, près de la casserole. Il a écouté sous le préau, pendant la chanson. Maman, j'ai un malaise. Un camarade a parlé tout bas. Tu as bien fait de raconter. Tu as écouté la maîtresse. Si tu as un malaise, tu viens nous le dire. Je raconte à la maison. Bravo, Nino. C'est du bon travail. Je t'écoute. On reste un moment. Maman écoute jusqu'au bout, sans couper. Le ventre de Nino se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15143,10 +16178,29 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Nino rejoint maman. Il a écouté à le préau, pendant la chanson. Il a eu un malaise. Il vient raconter à la maison.</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr"/>
+          <t>narrateur|Le soir, la maison sent la soupe.
+narrateur|La lampe fait un rond jaune.
+narrateur|Nino rejoint maman, près de la casserole.
+narrateur|Il a écouté sous le préau, pendant la chanson.
+enfant-m|Maman, j'ai un malaise.
+enfant-m|Un camarade a parlé tout bas.
+maman|Tu as bien fait de raconter.
+maman|Tu as écouté la maîtresse.
+papa|Si tu as un malaise, tu viens nous le dire.
+enfant-m|Je raconte à la maison.
+maman|Bravo, Nino.
+maman|C'est du bon travail.
+papa|Je t'écoute.
+papa|On reste un moment.
+narrateur|Maman écoute jusqu'au bout, sans couper.
+narrateur|Le ventre de Nino se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>soupe</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15171,7 +16225,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nino a écouté sous le préau, pendant la chanson. Puis il a raconté, à maman. Une goutte du préau brille encore. La chanson s'est tue, tout doux. Maman pose la main sur son épaule. J'ai écouté. Puis j'ai raconté. Bravo, Nino. Tu as fait du bon travail. On t'a écouté. Si malaise, tu reviens nous le dire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15311,7 +16365,18 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nino a écouté sous le préau, pendant la chanson.
+narrateur|Puis il a raconté, à maman.
+narrateur|Une goutte du préau brille encore.
+narrateur|La chanson s'est tue, tout doux.
+narrateur|Maman pose la main sur son épaule.
+enfant-m|J'ai écouté.
+enfant-m|Puis j'ai raconté.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+maman|On t'a écouté.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15339,7 +16404,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Nino rejoint papa. Il a écouté à le préau, pendant la chanson. Il a eu un malaise. Il vient raconter à la maison.</t>
+          <t>Le soir, la maison sent la soupe. La lampe fait un rond jaune. Nino rejoint papa, près du cacao. Il a écouté sous le préau, pendant la chanson. Papa, j'ai un malaise. Un mot m'a gêné, à l'école. Tu as bien fait de le dire. Tu as écouté la maîtresse. Si malaise, tu racontes à la maison. Je raconte à papa et maman. Bravo, Nino. Tu as fait du bon travail. On t'écoute. Ton ventre peut se desserrer. Le cacao fume encore, tout calme. Le ventre de Nino se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15479,10 +16544,29 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Nino rejoint papa. Il a écouté à le préau, pendant la chanson. Il a eu un malaise. Il vient raconter à la maison.</t>
-        </is>
-      </c>
-      <c r="AX84" t="inlineStr"/>
+          <t>narrateur|Le soir, la maison sent la soupe.
+narrateur|La lampe fait un rond jaune.
+narrateur|Nino rejoint papa, près du cacao.
+narrateur|Il a écouté sous le préau, pendant la chanson.
+enfant-m|Papa, j'ai un malaise.
+enfant-m|Un mot m'a gêné, à l'école.
+papa|Tu as bien fait de le dire.
+papa|Tu as écouté la maîtresse.
+maman|Si malaise, tu racontes à la maison.
+enfant-m|Je raconte à papa et maman.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+maman|On t'écoute.
+maman|Ton ventre peut se desserrer.
+narrateur|Le cacao fume encore, tout calme.
+narrateur|Le ventre de Nino se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>cacao</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15507,7 +16591,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nino a écouté sous le préau, pendant la chanson. Puis il a raconté, à papa. Une goutte du préau brille encore. La chanson s'est tue, tout doux. Papa souffle sur le cacao, tout doux. J'ai écouté. Puis j'ai raconté. Bravo, Nino. Tu as fait du bon travail. On t'a écouté. Si malaise, tu reviens nous le dire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15647,7 +16731,18 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nino a écouté sous le préau, pendant la chanson.
+narrateur|Puis il a raconté, à papa.
+narrateur|Une goutte du préau brille encore.
+narrateur|La chanson s'est tue, tout doux.
+narrateur|Papa souffle sur le cacao, tout doux.
+enfant-m|J'ai écouté.
+enfant-m|Puis j'ai raconté.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+maman|On t'a écouté.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15675,7 +16770,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Nino rejoint la sœur. Il a écouté à le préau, pendant la chanson. Il a eu un malaise. Il vient raconter à la maison.</t>
+          <t>Le soir, la maison sent la soupe. La lampe fait un rond jaune. Nino rejoint Sarah, près du bol de Sarah. Il a écouté sous le préau, pendant la chanson. Sarah, j'ai un malaise. Je t'écoute, Nino. Un camarade a chuchoté. Nino veut raconter. Tu as écouté la maîtresse. Si malaise, raconter à la maison. Je raconte à la maison. Bravo, les enfants. C'est du bon travail. Sarah serre la main de Nino, tout fort. Le ventre de Nino se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15815,10 +16910,28 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Le soir, Nino rejoint la sœur. Il a écouté à le préau, pendant la chanson. Il a eu un malaise. Il vient raconter à la maison.</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr"/>
+          <t>narrateur|Le soir, la maison sent la soupe.
+narrateur|La lampe fait un rond jaune.
+narrateur|Nino rejoint Sarah, près du bol de Sarah.
+narrateur|Il a écouté sous le préau, pendant la chanson.
+enfant-m|Sarah, j'ai un malaise.
+enfant-f|Je t'écoute, Nino.
+enfant-m|Un camarade a chuchoté.
+enfant-f|Nino veut raconter.
+maman|Tu as écouté la maîtresse.
+papa|Si malaise, raconter à la maison.
+enfant-m|Je raconte à la maison.
+maman|Bravo, les enfants.
+maman|C'est du bon travail.
+narrateur|Sarah serre la main de Nino, tout fort.
+narrateur|Le ventre de Nino se desserre, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>bol</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15843,7 +16956,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nino a écouté sous le préau, pendant la chanson. Puis il a raconté, à Sarah. Une goutte du préau brille encore. La chanson s'est tue, tout doux. Sarah pousse son bol vers Nino. J'ai écouté. Puis j'ai raconté. Bravo, Nino. Tu as fait du bon travail. On t'a écouté. Si malaise, tu reviens nous le dire. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -15983,7 +17096,18 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nino a écouté sous le préau, pendant la chanson.
+narrateur|Puis il a raconté, à Sarah.
+narrateur|Une goutte du préau brille encore.
+narrateur|La chanson s'est tue, tout doux.
+narrateur|Sarah pousse son bol vers Nino.
+enfant-m|J'ai écouté.
+enfant-m|Puis j'ai raconté.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+maman|On t'a écouté.
+maman|Si malaise, tu reviens nous le dire.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16005,7 +17129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16050,6 +17174,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-COL-007.xlsx
+++ b/stories/arbres/TREE-COL-007.xlsx
@@ -4645,17 +4645,17 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Le soir, le crayon de poche dépasse du manteau. Papa range les chaussures, le dos tourné. Regarde mes virgules ! Papa entend le mot virgules, pas le reste. Nino s'assoit, le crayon en l'air. Il attend qu'il se tourne. Je te vois. Montre-moi. À l'école, j'ai tracé les bottes, après l'attente. Papa pose le crayon à côté, sans le prendre. Le rond de la lampe est assez grand pour deux. Les bottes et le crayon dorment dans la lumière.</t>
+          <t>Le soir, le crayon de poche dépasse du manteau. Papa range les chaussures, le dos tourné. Regarde mes virgules ! Papa entend le mot virgules, pas le reste. Nino s'assoit, le crayon en l'air. Il attend qu'il se tourne. Je te vois. Montre-moi. À l'école, j'ai tracé les bottes, après l'attente. Papa pose le crayon à côté, sans le prendre. Le rond de la lampe est assez grand pour deux. Les bottes, le crayon et un croissant de buée dorment dans la lumière.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le soir, le crayon de poche dépasse du manteau. Papa range les chaussures, le dos tourné. Regarde mes virgules ! Papa entend le mot virgules, pas le reste. Nino s'assoit, le crayon en l'air. Il attend qu'il se tourne. Je te vois. Montre-moi. À l'école, j'ai tracé les bottes, après l'attente. Papa pose le crayon à côté, sans le prendre. Le rond de la lampe est assez grand pour deux. Les bottes et le crayon dorment dans la lumière.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le soir, le crayon de poche dépasse du manteau. Papa range les chaussures, le dos tourné. Regarde mes virgules ! Papa entend le mot virgules, pas le reste. Nino s'assoit, le crayon en l'air. Il attend qu'il se tourne. Je te vois. Montre-moi. À l'école, j'ai tracé les bottes, après l'attente. Papa pose le crayon à côté, sans le prendre. Le rond de la lampe est assez grand pour deux. Les bottes, le crayon et un croissant de buée dorment dans la lumière.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Le soir, le crayon de poche dépasse du manteau. Papa range les chaussures, le dos tourné. Regarde mes virgules ! Papa entend le mot virgules, pas le reste. Nino s'assoit, le crayon en l'air. Il attend qu'il se tourne. Je te vois. Montre-moi. À l'école, j'ai tracé les bottes, après l'attente. Papa pose le crayon à côté, sans le prendre. Le rond de la lampe est assez grand pour deux. Les bottes et le crayon dorment dans la lumière. [pause]</t>
+          <t>Le soir, le crayon de poche dépasse du manteau. Papa range les chaussures, le dos tourné. Regarde mes virgules ! Papa entend le mot virgules, pas le reste. Nino s'assoit, le crayon en l'air. Il attend qu'il se tourne. Je te vois. Montre-moi. À l'école, j'ai tracé les bottes, après l'attente. Papa pose le crayon à côté, sans le prendre. Le rond de la lampe est assez grand pour deux. Les bottes, le crayon et un croissant de buée dorment dans la lumière. [pause]</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
@@ -4800,7 +4800,7 @@
 enfant-m|À l'école, j'ai tracé les bottes, après l'attente.
 narrateur|Papa pose le crayon à côté, sans le prendre.
 maman|Le rond de la lampe est assez grand pour deux.
-narrateur|Les bottes et le crayon dorment dans la lumière.</t>
+narrateur|Les bottes, le crayon et un croissant de buée dorment dans la lumière.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -6163,17 +6163,17 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Le soir, papa chante en rangeant le manteau. Bottes, bottes ! Les deux voix se marchent dessus, près du tapis. Laisse-moi finir. Ensuite, ton couplet. Nino attend, un pied sur la laine. À l'école, j'ai trop chanté tôt. Le fil a cassé. Papa s'arrête pile, et penche l'oreille. Bottes, bottes, sur le tapis. Cette fois, ta note a toute la place. Les boucles vibrent, comme un petit tambour. On les pose près du radiateur, sur le dernier mot.</t>
+          <t>Le soir, papa chante en rangeant le manteau. Bottes, bottes ! Les deux voix se marchent dessus, près du tapis. Laisse-moi finir. Ensuite, ton couplet. Nino attend, un pied sur la laine. À l'école, j'ai trop chanté tôt. Le fil a cassé. Papa s'arrête pile, et penche l'oreille. Bottes, bottes, sur le tapis. Cette fois, ta note a toute la place. Les boucles vibrent. Un croissant de buée suit le rythme. On les pose près du radiateur, sur le dernier mot.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le soir, papa chante en rangeant le manteau. Bottes, bottes ! Les deux voix se marchent dessus, près du tapis. Laisse-moi finir. Ensuite, ton couplet. Nino attend, un pied sur la laine. À l'école, j'ai trop chanté tôt. Le fil a cassé. Papa s'arrête pile, et penche l'oreille. Bottes, bottes, sur le tapis. Cette fois, ta note a toute la place. Les boucles vibrent, comme un petit tambour. On les pose près du radiateur, sur le dernier mot.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le soir, papa chante en rangeant le manteau. Bottes, bottes ! Les deux voix se marchent dessus, près du tapis. Laisse-moi finir. Ensuite, ton couplet. Nino attend, un pied sur la laine. À l'école, j'ai trop chanté tôt. Le fil a cassé. Papa s'arrête pile, et penche l'oreille. Bottes, bottes, sur le tapis. Cette fois, ta note a toute la place. Les boucles vibrent. Un croissant de buée suit le rythme. On les pose près du radiateur, sur le dernier mot.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Le soir, papa chante en rangeant le manteau. Bottes, bottes ! Les deux voix se marchent dessus, près du tapis. Laisse-moi finir. Ensuite, ton couplet. Nino attend, un pied sur la laine. À l'école, j'ai trop chanté tôt. Le fil a cassé. Papa s'arrête pile, et penche l'oreille. Bottes, bottes, sur le tapis. Cette fois, ta note a toute la place. Les boucles vibrent, comme un petit tambour. On les pose près du radiateur, sur le dernier mot. [pause]</t>
+          <t>Le soir, papa chante en rangeant le manteau. Bottes, bottes ! Les deux voix se marchent dessus, près du tapis. Laisse-moi finir. Ensuite, ton couplet. Nino attend, un pied sur la laine. À l'école, j'ai trop chanté tôt. Le fil a cassé. Papa s'arrête pile, et penche l'oreille. Bottes, bottes, sur le tapis. Cette fois, ta note a toute la place. Les boucles vibrent. Un croissant de buée suit le rythme. On les pose près du radiateur, sur le dernier mot. [pause]</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
@@ -6318,7 +6318,8 @@
 narrateur|Papa s'arrête pile, et penche l'oreille.
 enfant-m|Bottes, bottes, sur le tapis.
 maman|Cette fois, ta note a toute la place.
-narrateur|Les boucles vibrent, comme un petit tambour.
+narrateur|Les boucles vibrent.
+narrateur|Un croissant de buée suit le rythme.
 papa|On les pose près du radiateur, sur le dernier mot.</t>
         </is>
       </c>
@@ -6351,17 +6352,17 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Nino a chanté les bottes, après le manteau. J'ai fini, puis toi. Merci d'avoir laissé le couplet de papa. Le fil n'a pas cassé, cette fois. Une note de la chanson reste dans la vapeur du cacao. Les boucles vibrent, puis s'arrêtent. Le moment où ça cassait, tu le dis ? Oui. Sur le tapis. Le radiateur n'a plus de tic, plus de refrain.</t>
+          <t>Nino a chanté les bottes, après le manteau. J'ai fini, puis toi. Merci d'avoir laissé le couplet de papa. Le fil n'a pas cassé, cette fois. Une note de la chanson reste dans la vapeur du cacao. Les boucles vibrent, puis s'arrêtent. Le moment où ça cassait, tu le dis ? Oui. Sur le tapis. Le croissant de buée quitte le radiateur, sans refrain.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nino a chanté les &lt;emphasis level="moderate"&gt;bottes&lt;/emphasis&gt;, après le manteau. J'ai fini, puis toi. Merci d'avoir laissé le couplet de papa. Le fil n'a pas cassé, cette fois. Une note de la chanson reste dans la vapeur du cacao. Les boucles vibrent, puis s'arrêtent. Le moment où ça cassait, tu le dis ? Oui. Sur le tapis. Le radiateur n'a plus de tic, plus de refrain.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nino a chanté les &lt;emphasis level="moderate"&gt;bottes&lt;/emphasis&gt;, après le manteau. J'ai fini, puis toi. Merci d'avoir laissé le couplet de papa. Le fil n'a pas cassé, cette fois. Une note de la chanson reste dans la vapeur du cacao. Les boucles vibrent, puis s'arrêtent. Le moment où ça cassait, tu le dis ? Oui. Sur le tapis. Le croissant de buée quitte le radiateur, sans refrain.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nino a chanté les &lt;emphasis&gt;bottes&lt;/emphasis&gt;, après le manteau. J'ai fini, puis toi. Merci d'avoir laissé le couplet de papa. Le fil n'a pas cassé, cette fois. Une note de la chanson reste dans la vapeur du cacao. Les boucles vibrent, puis s'arrêtent. Le moment où ça cassait, tu le dis ? Oui. Sur le tapis. Le radiateur n'a plus de tic, plus de refrain.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nino a chanté les &lt;emphasis&gt;bottes&lt;/emphasis&gt;, après le manteau. J'ai fini, puis toi. Merci d'avoir laissé le couplet de papa. Le fil n'a pas cassé, cette fois. Une note de la chanson reste dans la vapeur du cacao. Les boucles vibrent, puis s'arrêtent. Le moment où ça cassait, tu le dis ? Oui. Sur le tapis. Le croissant de buée quitte le radiateur, sans refrain.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
@@ -6508,7 +6509,7 @@
 papa|Le moment où ça cassait, tu le dis ?
 enfant-m|Oui.
 enfant-m|Sur le tapis.
-narrateur|Le radiateur n'a plus de tic, plus de refrain.</t>
+narrateur|Le croissant de buée quitte le radiateur, sans refrain.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
@@ -6920,17 +6921,17 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Nino grimpe sur la chaise, près de la table. Le bois est lisse, un peu froid. Ma phrase, tout de suite ! La chaise racle. Le bruit couvre les mots. La maîtresse lève les yeux, puis reprend. Nino se rassoit, le ventre serré. Le sourire de Nino disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Il pose les mains à plat, sur le bois. Il attend que la racle se taise. Je m'accroupis, près des pieds de la chaise. Ta phrase, on la prend dans le calme ? Oui. Un camarade a parlé trop fort. Ça m'a pincé, ici. Merci d'avoir gardé tes mains sur la table. Un crayon roule, et s'arrête contre sa manche.</t>
+          <t>Nino grimpe sur la chaise, près de la table. Le bois est lisse, un peu froid. Ma phrase, tout de suite ! La chaise racle. Le bruit couvre les mots. La maîtresse lève les yeux, puis reprend. Nino se rassoit, le ventre serré. Le sourire de Nino disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Il pose les mains à plat, sur le bois. Il attend que la racle se taise. Je m'accroupis, près des pieds de la chaise. Ta phrase, on la prend sans le bruit ? Oui. Un camarade a parlé trop fort. Ça m'a pincé, ici. Merci d'avoir gardé tes mains sur la table. Un crayon roule, et s'arrête contre sa manche.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino grimpe sur la chaise, près de la table. Le bois est lisse, un peu froid. Ma phrase, tout de suite ! La chaise racle. Le bruit couvre les mots. La maîtresse lève les yeux, puis reprend. Nino se rassoit, le ventre serré. Le sourire de Nino disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Il pose les mains à plat, sur le bois. Il attend que la racle se taise. Je m'accroupis, près des pieds de la chaise. Ta phrase, on la prend dans le calme ? Oui. Un camarade a parlé trop fort. Ça m'a pincé, ici. Merci d'avoir gardé tes mains sur la table. Un crayon roule, et s'arrête contre sa manche.&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino grimpe sur la chaise, près de la table. Le bois est lisse, un peu froid. Ma phrase, tout de suite ! La chaise racle. Le bruit couvre les mots. La maîtresse lève les yeux, puis reprend. Nino se rassoit, le ventre serré. Le sourire de Nino disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Il pose les mains à plat, sur le bois. Il attend que la racle se taise. Je m'accroupis, près des pieds de la chaise. Ta phrase, on la prend sans le bruit ? Oui. Un camarade a parlé trop fort. Ça m'a pincé, ici. Merci d'avoir gardé tes mains sur la table. Un crayon roule, et s'arrête contre sa manche.&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Nino grimpe sur la chaise, près de la table. Le bois est lisse, un peu froid. Ma phrase, tout de suite ! La chaise racle. Le bruit couvre les mots. La maîtresse lève les yeux, puis reprend. Nino se rassoit, le ventre serré. Le sourire de Nino disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Il pose les mains à plat, sur le bois. Il attend que la racle se taise. Je m'accroupis, près des pieds de la chaise. Ta phrase, on la prend dans le calme ? Oui. Un camarade a parlé trop fort. Ça m'a pincé, ici. Merci d'avoir gardé tes mains sur la table. Un crayon roule, et s'arrête contre sa manche. [pause]</t>
+          <t>Nino grimpe sur la chaise, près de la table. Le bois est lisse, un peu froid. Ma phrase, tout de suite ! La chaise racle. Le bruit couvre les mots. La maîtresse lève les yeux, puis reprend. Nino se rassoit, le ventre serré. Le sourire de Nino disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Il pose les mains à plat, sur le bois. Il attend que la racle se taise. Je m'accroupis, près des pieds de la chaise. Ta phrase, on la prend sans le bruit ? Oui. Un camarade a parlé trop fort. Ça m'a pincé, ici. Merci d'avoir gardé tes mains sur la table. Un crayon roule, et s'arrête contre sa manche. [pause]</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
@@ -7076,7 +7077,7 @@
 narrateur|Il pose les mains à plat, sur le bois.
 narrateur|Il attend que la racle se taise.
 papa|Je m'accroupis, près des pieds de la chaise.
-maman|Ta phrase, on la prend dans le calme ?
+maman|Ta phrase, on la prend sans le bruit ?
 enfant-m|Oui.
 enfant-m|Un camarade a parlé trop fort.
 enfant-m|Ça m'a pincé, ici.
@@ -16464,17 +16465,17 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Nino entre avec une note du préau, trop haute. La casserole répond, trop basse. C'est ma chanson de gouttes ! La mienne, c'est le thym. Une après l'autre. Nino se tait. Une botte claque, puis plus. Sous le toit, j'ai chanté dans l'eau. Après, dans le creux. Chante-moi le creux, ici. Nino glisse sa note. La vapeur danse, sans ploc. On pose les bottes sur le dernier mot. Le couplet rentre dans la vapeur, et s'y perd. Cette fois, ma note a eu le silence.</t>
+          <t>Le soir, Nino entre avec une note du préau, trop haute. La casserole répond, trop basse. C'est ma chanson de gouttes ! La mienne, c'est le thym. Une après l'autre. Nino se tait. Une botte claque, puis plus. Sous le toit, j'ai chanté dans l'eau. Après, dans le creux. Chante-moi le creux, ici. Nino glisse sa note. La vapeur danse, sans ploc. On pose les bottes sur le dernier mot. Le couplet rentre dans le croissant de vapeur, et s'y perd. Cette fois, ma note a eu le silence.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le soir, Nino entre avec une note du préau, trop haute. La casserole répond, trop basse. C'est ma chanson de gouttes ! La mienne, c'est le thym. Une après l'autre. Nino se tait. Une botte claque, puis plus. Sous le toit, j'ai chanté dans l'eau. Après, dans le creux. Chante-moi le creux, ici. Nino glisse sa note. La vapeur danse, sans ploc. On pose les bottes sur le dernier mot. Le couplet rentre dans la vapeur, et s'y perd. Cette fois, ma note a eu le silence.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le soir, Nino entre avec une note du préau, trop haute. La casserole répond, trop basse. C'est ma chanson de gouttes ! La mienne, c'est le thym. Une après l'autre. Nino se tait. Une botte claque, puis plus. Sous le toit, j'ai chanté dans l'eau. Après, dans le creux. Chante-moi le creux, ici. Nino glisse sa note. La vapeur danse, sans ploc. On pose les bottes sur le dernier mot. Le couplet rentre dans le croissant de vapeur, et s'y perd. Cette fois, ma note a eu le silence.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Nino entre avec une note du préau, trop haute. La casserole répond, trop basse. C'est ma chanson de gouttes ! La mienne, c'est le thym. Une après l'autre. Nino se tait. Une botte claque, puis plus. Sous le toit, j'ai chanté dans l'eau. Après, dans le creux. Chante-moi le creux, ici. Nino glisse sa note. La vapeur danse, sans ploc. On pose les bottes sur le dernier mot. Le couplet rentre dans la vapeur, et s'y perd. Cette fois, ma note a eu le silence. [pause]</t>
+          <t>Le soir, Nino entre avec une note du préau, trop haute. La casserole répond, trop basse. C'est ma chanson de gouttes ! La mienne, c'est le thym. Une après l'autre. Nino se tait. Une botte claque, puis plus. Sous le toit, j'ai chanté dans l'eau. Après, dans le creux. Chante-moi le creux, ici. Nino glisse sa note. La vapeur danse, sans ploc. On pose les bottes sur le dernier mot. Le couplet rentre dans le croissant de vapeur, et s'y perd. Cette fois, ma note a eu le silence. [pause]</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr"/>
@@ -16621,7 +16622,7 @@
 narrateur|Nino glisse sa note.
 narrateur|La vapeur danse, sans ploc.
 papa|On pose les bottes sur le dernier mot.
-narrateur|Le couplet rentre dans la vapeur, et s'y perd.
+narrateur|Le couplet rentre dans le croissant de vapeur, et s'y perd.
 enfant-m|Cette fois, ma note a eu le silence.</t>
         </is>
       </c>
@@ -16654,17 +16655,17 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Nino a chanté le creux, après le thym. J'ai eu ta note. Merci. Les bottes attendent le dernier mot. Dans l'eau, puis dans le silence. Le couplet rentre dans la vapeur, et s'y perd. La casserole ne répond plus, trop basse. Tu gardes la note trop haute ? Surtout celle-là. Une botte claque, puis plus.</t>
+          <t>Nino a chanté le creux, après le thym. J'ai eu ta note. Merci. Les bottes attendent le dernier mot. Dans l'eau, puis dans le silence. Le couplet rentre dans la vapeur, et s'y perd. La casserole ne répond plus, trop basse. Tu gardes la note trop haute ? Surtout celle-là. Une botte claque. Le croissant de buée s'en va.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nino a chanté le creux, après le thym. J'ai eu ta note. Merci. Les &lt;emphasis level="moderate"&gt;bottes&lt;/emphasis&gt; attendent le dernier mot. Dans l'eau, puis dans le silence. Le couplet rentre dans la vapeur, et s'y perd. La casserole ne répond plus, trop basse. Tu gardes la note trop haute ? Surtout celle-là. Une botte claque, puis plus.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nino a chanté le creux, après le thym. J'ai eu ta note. Merci. Les &lt;emphasis level="moderate"&gt;bottes&lt;/emphasis&gt; attendent le dernier mot. Dans l'eau, puis dans le silence. Le couplet rentre dans la vapeur, et s'y perd. La casserole ne répond plus, trop basse. Tu gardes la note trop haute ? Surtout celle-là. Une botte claque. Le croissant de buée s'en va.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nino a chanté le creux, après le thym. J'ai eu ta note. Merci. Les &lt;emphasis&gt;bottes&lt;/emphasis&gt; attendent le dernier mot. Dans l'eau, puis dans le silence. Le couplet rentre dans la vapeur, et s'y perd. La casserole ne répond plus, trop basse. Tu gardes la note trop haute ? Surtout celle-là. Une botte claque, puis plus.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nino a chanté le creux, après le thym. J'ai eu ta note. Merci. Les &lt;emphasis&gt;bottes&lt;/emphasis&gt; attendent le dernier mot. Dans l'eau, puis dans le silence. Le couplet rentre dans la vapeur, et s'y perd. La casserole ne répond plus, trop basse. Tu gardes la note trop haute ? Surtout celle-là. Une botte claque. Le croissant de buée s'en va.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr"/>
@@ -16811,7 +16812,8 @@
 narrateur|La casserole ne répond plus, trop basse.
 maman|Tu gardes la note trop haute ?
 enfant-m|Surtout celle-là.
-narrateur|Une botte claque, puis plus.</t>
+narrateur|Une botte claque.
+narrateur|Le croissant de buée s'en va.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
@@ -17224,17 +17226,17 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Sarah tapote le bol, un, deux. C'est le rythme du préau ! Il chante par-dessus. Le bol tressaute. Un tap, puis l'autre. Le tien après le mien. Nino compte. Il glisse sa note dans le trou. J'ai chanté dans l'eau. Après, dans le silence. On a le silence, ici. Sarah pousse le bol. Le bonnet rouge ne goutte plus. Toi, tu as le creux. Moi, le bonnet. Sarah chante tout bas, une fois, puis le bol se tait. Les bottes s'endorment, légères, près du bois.</t>
+          <t>Le soir, Sarah tapote le bol, un, deux. C'est le rythme du préau ! Il chante par-dessus. Le bol tressaute. Un tap, puis l'autre. Le tien après le mien. Nino compte. Il glisse sa note dans le trou. J'ai chanté dans l'eau. Après, dans le silence. On a le silence, ici. Sarah pousse le bol. Le bonnet rouge ne goutte plus. Toi, tu as le creux. Moi, le bonnet. Sarah chante tout bas, une fois, puis le bol se tait. Les bottes s'endorment près du croissant de buée.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le soir, Sarah tapote le bol, un, deux. C'est le rythme du préau ! Il chante par-dessus. Le bol tressaute. Un tap, puis l'autre. Le tien après le mien. Nino compte. Il glisse sa note dans le trou. J'ai chanté dans l'eau. Après, dans le silence. On a le silence, ici. Sarah pousse le bol. Le bonnet rouge ne goutte plus. Toi, tu as le creux. Moi, le bonnet. Sarah chante tout bas, une fois, puis le bol se tait. Les bottes s'endorment, légères, près du bois.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le soir, Sarah tapote le bol, un, deux. C'est le rythme du préau ! Il chante par-dessus. Le bol tressaute. Un tap, puis l'autre. Le tien après le mien. Nino compte. Il glisse sa note dans le trou. J'ai chanté dans l'eau. Après, dans le silence. On a le silence, ici. Sarah pousse le bol. Le bonnet rouge ne goutte plus. Toi, tu as le creux. Moi, le bonnet. Sarah chante tout bas, une fois, puis le bol se tait. Les bottes s'endorment près du croissant de buée.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Sarah tapote le bol, un, deux. C'est le rythme du préau ! Il chante par-dessus. Le bol tressaute. Un tap, puis l'autre. Le tien après le mien. Nino compte. Il glisse sa note dans le trou. J'ai chanté dans l'eau. Après, dans le silence. On a le silence, ici. Sarah pousse le bol. Le bonnet rouge ne goutte plus. Toi, tu as le creux. Moi, le bonnet. Sarah chante tout bas, une fois, puis le bol se tait. Les bottes s'endorment, légères, près du bois. [pause]</t>
+          <t>Le soir, Sarah tapote le bol, un, deux. C'est le rythme du préau ! Il chante par-dessus. Le bol tressaute. Un tap, puis l'autre. Le tien après le mien. Nino compte. Il glisse sa note dans le trou. J'ai chanté dans l'eau. Après, dans le silence. On a le silence, ici. Sarah pousse le bol. Le bonnet rouge ne goutte plus. Toi, tu as le creux. Moi, le bonnet. Sarah chante tout bas, une fois, puis le bol se tait. Les bottes s'endorment près du croissant de buée. [pause]</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr"/>
@@ -17384,7 +17386,7 @@
 enfant-f|Toi, tu as le creux.
 enfant-f|Moi, le bonnet.
 narrateur|Sarah chante tout bas, une fois, puis le bol se tait.
-narrateur|Les bottes s'endorment, légères, près du bois.</t>
+narrateur|Les bottes s'endorment près du croissant de buée.</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
@@ -17416,17 +17418,17 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Nino a glissé sa note dans le trou de Sarah. Toi, tu as le creux. Moi, le bonnet. On a le silence, ici. Merci, les deux rythmes. Sarah chante tout bas, une fois, puis le bol se tait. Les bottes s'endorment, légères, près du bois. J'ai chanté dans l'eau. Après, dans le silence. Moi, j'ai tapoté, puis j'ai écouté. Le bonnet rouge ne goutte plus, plus du tout.</t>
+          <t>Nino a glissé sa note dans le trou de Sarah. Toi, tu as le creux. Moi, le bonnet. On a le silence, ici. Merci, les deux rythmes. Sarah chante tout bas, une fois, puis le bol se tait. Les bottes s'endorment, légères, près du bois. J'ai chanté dans l'eau. Après, dans le silence. Moi, j'ai tapoté, puis j'ai écouté. Le croissant de buée s'endort sur le bonnet rouge.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nino a glissé sa note dans le trou de Sarah. Toi, tu as le creux. Moi, le bonnet. On a le silence, ici. Merci, les deux rythmes. Sarah chante tout bas, une fois, puis le bol se tait. Les &lt;emphasis level="moderate"&gt;bottes&lt;/emphasis&gt; s'endorment, légères, près du bois. J'ai chanté dans l'eau. Après, dans le silence. Moi, j'ai tapoté, puis j'ai écouté. Le bonnet rouge ne goutte plus, plus du tout.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nino a glissé sa note dans le trou de Sarah. Toi, tu as le creux. Moi, le bonnet. On a le silence, ici. Merci, les deux rythmes. Sarah chante tout bas, une fois, puis le bol se tait. Les &lt;emphasis level="moderate"&gt;bottes&lt;/emphasis&gt; s'endorment, légères, près du bois. J'ai chanté dans l'eau. Après, dans le silence. Moi, j'ai tapoté, puis j'ai écouté. Le croissant de buée s'endort sur le bonnet rouge.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nino a glissé sa note dans le trou de Sarah. Toi, tu as le creux. Moi, le bonnet. On a le silence, ici. Merci, les deux rythmes. Sarah chante tout bas, une fois, puis le bol se tait. Les &lt;emphasis&gt;bottes&lt;/emphasis&gt; s'endorment, légères, près du bois. J'ai chanté dans l'eau. Après, dans le silence. Moi, j'ai tapoté, puis j'ai écouté. Le bonnet rouge ne goutte plus, plus du tout.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nino a glissé sa note dans le trou de Sarah. Toi, tu as le creux. Moi, le bonnet. On a le silence, ici. Merci, les deux rythmes. Sarah chante tout bas, une fois, puis le bol se tait. Les &lt;emphasis&gt;bottes&lt;/emphasis&gt; s'endorment, légères, près du bois. J'ai chanté dans l'eau. Après, dans le silence. Moi, j'ai tapoté, puis j'ai écouté. Le croissant de buée s'endort sur le bonnet rouge.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr"/>
@@ -17574,7 +17576,7 @@
 enfant-m|J'ai chanté dans l'eau.
 enfant-m|Après, dans le silence.
 enfant-f|Moi, j'ai tapoté, puis j'ai écouté.
-narrateur|Le bonnet rouge ne goutte plus, plus du tout.</t>
+narrateur|Le croissant de buée s'endort sur le bonnet rouge.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
@@ -17600,7 +17602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17664,6 +17666,13 @@
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
